--- a/examples/medibec/deliverables/MediBec_CyberRiskGuardian_Workbook_30_Budget.xlsx
+++ b/examples/medibec/deliverables/MediBec_CyberRiskGuardian_Workbook_30_Budget.xlsx
@@ -2,10 +2,10 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <fileVersion appName="Calc"/>
-  <workbookPr backupFile="false" showObjects="all" date1904="false"/>
+  <workbookPr backupFile="false" showObjects="all" dateCompatibility="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="600" firstSheet="0" activeTab="0"/>
   </bookViews>
   <sheets>
     <sheet name="README" sheetId="1" state="visible" r:id="rId3"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/comments4.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:v2="http://schemas.openxmlformats.org/spreadsheetml/2006/main/v2" mc:Ignorable="v2">
   <authors>
     <author>Unknown Author</author>
   </authors>
@@ -50,6 +50,27 @@
           <t xml:space="preserve">Phishing is constant and attempts are increasing; lures already observed. Evidence: E4, E6</t>
         </r>
       </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>1</xdr:col>
+                <xdr:colOff>35</xdr:colOff>
+                <xdr:row>0</xdr:row>
+                <xdr:rowOff>2</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>2</xdr:col>
+                <xdr:colOff>-265</xdr:colOff>
+                <xdr:row>3</xdr:row>
+                <xdr:rowOff>10</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
     </comment>
     <comment ref="C5" authorId="0">
       <text>
@@ -62,6 +83,27 @@
           <t xml:space="preserve">Healthcare is a sustained ransomware target; attempts rising. Evidence: E4</t>
         </r>
       </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>1</xdr:col>
+                <xdr:colOff>35</xdr:colOff>
+                <xdr:row>0</xdr:row>
+                <xdr:rowOff>2</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>2</xdr:col>
+                <xdr:colOff>-265</xdr:colOff>
+                <xdr:row>3</xdr:row>
+                <xdr:rowOff>7</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
     </comment>
     <comment ref="C6" authorId="0">
       <text>
@@ -74,6 +116,27 @@
           <t xml:space="preserve">Conditional on an intrusion reaching administrative level (S1/S2). Evidence: E4, E6</t>
         </r>
       </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>1</xdr:col>
+                <xdr:colOff>35</xdr:colOff>
+                <xdr:row>0</xdr:row>
+                <xdr:rowOff>2</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>2</xdr:col>
+                <xdr:colOff>-265</xdr:colOff>
+                <xdr:row>3</xdr:row>
+                <xdr:rowOff>10</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
     </comment>
     <comment ref="C7" authorId="0">
       <text>
@@ -86,6 +149,27 @@
           <t xml:space="preserve">Cloud storage is continuously scanned. Evidence: E4</t>
         </r>
       </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>1</xdr:col>
+                <xdr:colOff>35</xdr:colOff>
+                <xdr:row>0</xdr:row>
+                <xdr:rowOff>2</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>2</xdr:col>
+                <xdr:colOff>-265</xdr:colOff>
+                <xdr:row>3</xdr:row>
+                <xdr:rowOff>7</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
     </comment>
     <comment ref="C8" authorId="0">
       <text>
@@ -98,6 +182,27 @@
           <t xml:space="preserve">Insider snooping is recurrent in healthcare; service-account anomaly observed. Evidence: E6</t>
         </r>
       </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>1</xdr:col>
+                <xdr:colOff>35</xdr:colOff>
+                <xdr:row>0</xdr:row>
+                <xdr:rowOff>2</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>2</xdr:col>
+                <xdr:colOff>-265</xdr:colOff>
+                <xdr:row>3</xdr:row>
+                <xdr:rowOff>25</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
     </comment>
     <comment ref="C9" authorId="0">
       <text>
@@ -110,6 +215,27 @@
           <t xml:space="preserve">Edge-device exploitation campaigns are frequent. Evidence: E4</t>
         </r>
       </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>1</xdr:col>
+                <xdr:colOff>35</xdr:colOff>
+                <xdr:row>0</xdr:row>
+                <xdr:rowOff>2</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>2</xdr:col>
+                <xdr:colOff>-265</xdr:colOff>
+                <xdr:row>3</xdr:row>
+                <xdr:rowOff>7</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
     </comment>
     <comment ref="C10" authorId="0">
       <text>
@@ -122,6 +248,27 @@
           <t xml:space="preserve">Targeting of devices is less frequent than IT, but collateral infection is common. Evidence: E4</t>
         </r>
       </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>1</xdr:col>
+                <xdr:colOff>35</xdr:colOff>
+                <xdr:row>0</xdr:row>
+                <xdr:rowOff>2</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>2</xdr:col>
+                <xdr:colOff>-265</xdr:colOff>
+                <xdr:row>3</xdr:row>
+                <xdr:rowOff>10</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
     </comment>
     <comment ref="C11" authorId="0">
       <text>
@@ -134,6 +281,27 @@
           <t xml:space="preserve">Attempts ongoing; some will pass perimeter controls. Evidence: E4</t>
         </r>
       </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>1</xdr:col>
+                <xdr:colOff>35</xdr:colOff>
+                <xdr:row>0</xdr:row>
+                <xdr:rowOff>2</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>2</xdr:col>
+                <xdr:colOff>-265</xdr:colOff>
+                <xdr:row>3</xdr:row>
+                <xdr:rowOff>7</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
     </comment>
     <comment ref="C12" authorId="0">
       <text>
@@ -146,6 +314,27 @@
           <t xml:space="preserve">Supply-chain attacks on healthcare vendors are recurrent. Evidence: E7</t>
         </r>
       </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>1</xdr:col>
+                <xdr:colOff>35</xdr:colOff>
+                <xdr:row>0</xdr:row>
+                <xdr:rowOff>2</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>2</xdr:col>
+                <xdr:colOff>-265</xdr:colOff>
+                <xdr:row>3</xdr:row>
+                <xdr:rowOff>7</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
     </comment>
     <comment ref="C13" authorId="0">
       <text>
@@ -158,6 +347,27 @@
           <t xml:space="preserve">Integrity attacks are rarer than theft or encryption. Evidence: E4</t>
         </r>
       </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>1</xdr:col>
+                <xdr:colOff>35</xdr:colOff>
+                <xdr:row>0</xdr:row>
+                <xdr:rowOff>2</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>2</xdr:col>
+                <xdr:colOff>-265</xdr:colOff>
+                <xdr:row>3</xdr:row>
+                <xdr:rowOff>7</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
     </comment>
     <comment ref="C14" authorId="0">
       <text>
@@ -170,6 +380,27 @@
           <t xml:space="preserve">Secret leakage is common where development occurs; MediBec's development footprint is uncertain. Evidence: E3, E7</t>
         </r>
       </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>1</xdr:col>
+                <xdr:colOff>35</xdr:colOff>
+                <xdr:row>0</xdr:row>
+                <xdr:rowOff>2</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>2</xdr:col>
+                <xdr:colOff>-265</xdr:colOff>
+                <xdr:row>4</xdr:row>
+                <xdr:rowOff>9</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
     </comment>
     <comment ref="C15" authorId="0">
       <text>
@@ -182,6 +413,27 @@
           <t xml:space="preserve">Requires physical proximity; clinics have public waiting rooms. Evidence: E1</t>
         </r>
       </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>1</xdr:col>
+                <xdr:colOff>35</xdr:colOff>
+                <xdr:row>0</xdr:row>
+                <xdr:rowOff>2</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>2</xdr:col>
+                <xdr:colOff>-265</xdr:colOff>
+                <xdr:row>3</xdr:row>
+                <xdr:rowOff>7</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
     </comment>
     <comment ref="C16" authorId="0">
       <text>
@@ -194,6 +446,27 @@
           <t xml:space="preserve">DDoS campaigns against healthcare occur; MediBec profile moderate. Evidence: E4</t>
         </r>
       </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>1</xdr:col>
+                <xdr:colOff>35</xdr:colOff>
+                <xdr:row>0</xdr:row>
+                <xdr:rowOff>2</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>2</xdr:col>
+                <xdr:colOff>-265</xdr:colOff>
+                <xdr:row>3</xdr:row>
+                <xdr:rowOff>10</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
     </comment>
     <comment ref="C17" authorId="0">
       <text>
@@ -206,6 +479,27 @@
           <t xml:space="preserve">BEC is among the most frequent fraud types; billing staff already targeted. Evidence: E6</t>
         </r>
       </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>1</xdr:col>
+                <xdr:colOff>35</xdr:colOff>
+                <xdr:row>0</xdr:row>
+                <xdr:rowOff>2</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>2</xdr:col>
+                <xdr:colOff>-265</xdr:colOff>
+                <xdr:row>3</xdr:row>
+                <xdr:rowOff>10</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
     </comment>
     <comment ref="C18" authorId="0">
       <text>
@@ -218,6 +512,27 @@
           <t xml:space="preserve">Across 10 clinics, some device loss each year is near certain. Evidence: E1, E2</t>
         </r>
       </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>1</xdr:col>
+                <xdr:colOff>35</xdr:colOff>
+                <xdr:row>0</xdr:row>
+                <xdr:rowOff>2</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>2</xdr:col>
+                <xdr:colOff>-265</xdr:colOff>
+                <xdr:row>3</xdr:row>
+                <xdr:rowOff>7</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
     </comment>
     <comment ref="C19" authorId="0">
       <text>
@@ -230,6 +545,27 @@
           <t xml:space="preserve">Multi-hour outages of a single hub occur over a 12-month horizon. Evidence: E2</t>
         </r>
       </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>1</xdr:col>
+                <xdr:colOff>35</xdr:colOff>
+                <xdr:row>0</xdr:row>
+                <xdr:rowOff>2</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>2</xdr:col>
+                <xdr:colOff>-265</xdr:colOff>
+                <xdr:row>3</xdr:row>
+                <xdr:rowOff>7</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
     </comment>
     <comment ref="C20" authorId="0">
       <text>
@@ -242,6 +578,27 @@
           <t xml:space="preserve">Local storage in 10 clinics; insiders and intruders both relevant. Evidence: E2, E4</t>
         </r>
       </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>1</xdr:col>
+                <xdr:colOff>35</xdr:colOff>
+                <xdr:row>0</xdr:row>
+                <xdr:rowOff>2</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>2</xdr:col>
+                <xdr:colOff>-265</xdr:colOff>
+                <xdr:row>3</xdr:row>
+                <xdr:rowOff>10</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
     </comment>
     <comment ref="C21" authorId="0">
       <text>
@@ -254,6 +611,27 @@
           <t xml:space="preserve">Public applications are constantly probed. Evidence: E8</t>
         </r>
       </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>1</xdr:col>
+                <xdr:colOff>35</xdr:colOff>
+                <xdr:row>0</xdr:row>
+                <xdr:rowOff>2</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>2</xdr:col>
+                <xdr:colOff>-265</xdr:colOff>
+                <xdr:row>3</xdr:row>
+                <xdr:rowOff>7</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
     </comment>
     <comment ref="C22" authorId="0">
       <text>
@@ -266,6 +644,27 @@
           <t xml:space="preserve">Rare but high-impact events. Evidence: E7</t>
         </r>
       </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>1</xdr:col>
+                <xdr:colOff>35</xdr:colOff>
+                <xdr:row>0</xdr:row>
+                <xdr:rowOff>2</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>2</xdr:col>
+                <xdr:colOff>-265</xdr:colOff>
+                <xdr:row>3</xdr:row>
+                <xdr:rowOff>7</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
     </comment>
     <comment ref="C23" authorId="0">
       <text>
@@ -278,6 +677,27 @@
           <t xml:space="preserve">AiTM kits and consent phishing are widespread. Evidence: E4</t>
         </r>
       </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>1</xdr:col>
+                <xdr:colOff>35</xdr:colOff>
+                <xdr:row>0</xdr:row>
+                <xdr:rowOff>2</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>2</xdr:col>
+                <xdr:colOff>-265</xdr:colOff>
+                <xdr:row>3</xdr:row>
+                <xdr:rowOff>7</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
     </comment>
     <comment ref="C24" authorId="0">
       <text>
@@ -290,6 +710,27 @@
           <t xml:space="preserve">Human error is near certain across 10 clinics in 12 months. Evidence: E1</t>
         </r>
       </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>1</xdr:col>
+                <xdr:colOff>35</xdr:colOff>
+                <xdr:row>0</xdr:row>
+                <xdr:rowOff>2</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>2</xdr:col>
+                <xdr:colOff>-265</xdr:colOff>
+                <xdr:row>3</xdr:row>
+                <xdr:rowOff>7</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
     </comment>
     <comment ref="C25" authorId="0">
       <text>
@@ -299,9 +740,30 @@
             <rFont val="Arial"/>
             <family val="2"/>
           </rPr>
-          <t xml:space="preserve">Opportunistic; depends on telehealth volume (Evidence gap). Evidence: E2</t>
+          <t xml:space="preserve">Opportunistic; depends on telehealth volume (Information gap). Evidence: E2</t>
         </r>
       </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>1</xdr:col>
+                <xdr:colOff>35</xdr:colOff>
+                <xdr:row>0</xdr:row>
+                <xdr:rowOff>2</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>2</xdr:col>
+                <xdr:colOff>-265</xdr:colOff>
+                <xdr:row>3</xdr:row>
+                <xdr:rowOff>7</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
     </comment>
     <comment ref="C26" authorId="0">
       <text>
@@ -314,6 +776,27 @@
           <t xml:space="preserve">Continuous internet scanning and password attacks. Evidence: E4</t>
         </r>
       </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>1</xdr:col>
+                <xdr:colOff>35</xdr:colOff>
+                <xdr:row>0</xdr:row>
+                <xdr:rowOff>2</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>2</xdr:col>
+                <xdr:colOff>-265</xdr:colOff>
+                <xdr:row>3</xdr:row>
+                <xdr:rowOff>7</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
     </comment>
     <comment ref="C27" authorId="0">
       <text>
@@ -326,6 +809,27 @@
           <t xml:space="preserve">External media is imported routinely. Evidence: E2</t>
         </r>
       </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>1</xdr:col>
+                <xdr:colOff>35</xdr:colOff>
+                <xdr:row>0</xdr:row>
+                <xdr:rowOff>2</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>2</xdr:col>
+                <xdr:colOff>-265</xdr:colOff>
+                <xdr:row>3</xdr:row>
+                <xdr:rowOff>7</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
     </comment>
     <comment ref="C28" authorId="0">
       <text>
@@ -338,6 +842,27 @@
           <t xml:space="preserve">Disposals occur every year. Evidence: E2</t>
         </r>
       </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>1</xdr:col>
+                <xdr:colOff>35</xdr:colOff>
+                <xdr:row>0</xdr:row>
+                <xdr:rowOff>2</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>2</xdr:col>
+                <xdr:colOff>-265</xdr:colOff>
+                <xdr:row>3</xdr:row>
+                <xdr:rowOff>7</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
     </comment>
     <comment ref="C29" authorId="0">
       <text>
@@ -350,6 +875,27 @@
           <t xml:space="preserve">Generative-AI use among clinicians is widespread by 2026. Evidence: E1</t>
         </r>
       </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>1</xdr:col>
+                <xdr:colOff>35</xdr:colOff>
+                <xdr:row>0</xdr:row>
+                <xdr:rowOff>2</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>2</xdr:col>
+                <xdr:colOff>-265</xdr:colOff>
+                <xdr:row>3</xdr:row>
+                <xdr:rowOff>7</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
     </comment>
     <comment ref="C30" authorId="0">
       <text>
@@ -362,6 +908,27 @@
           <t xml:space="preserve">Help-desk social engineering is an active technique against healthcare. Evidence: E4</t>
         </r>
       </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>1</xdr:col>
+                <xdr:colOff>35</xdr:colOff>
+                <xdr:row>0</xdr:row>
+                <xdr:rowOff>2</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>2</xdr:col>
+                <xdr:colOff>-265</xdr:colOff>
+                <xdr:row>3</xdr:row>
+                <xdr:rowOff>10</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
     </comment>
     <comment ref="C31" authorId="0">
       <text>
@@ -374,6 +941,27 @@
           <t xml:space="preserve">Malicious privileged insiders are rare. Evidence: E3</t>
         </r>
       </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>1</xdr:col>
+                <xdr:colOff>35</xdr:colOff>
+                <xdr:row>0</xdr:row>
+                <xdr:rowOff>2</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>2</xdr:col>
+                <xdr:colOff>-265</xdr:colOff>
+                <xdr:row>3</xdr:row>
+                <xdr:rowOff>7</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
     </comment>
     <comment ref="C32" authorId="0">
       <text>
@@ -386,6 +974,27 @@
           <t xml:space="preserve">Requires internal position and intent. Evidence: E2</t>
         </r>
       </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>1</xdr:col>
+                <xdr:colOff>35</xdr:colOff>
+                <xdr:row>0</xdr:row>
+                <xdr:rowOff>2</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>2</xdr:col>
+                <xdr:colOff>-265</xdr:colOff>
+                <xdr:row>3</xdr:row>
+                <xdr:rowOff>7</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
     </comment>
     <comment ref="C33" authorId="0">
       <text>
@@ -398,6 +1007,27 @@
           <t xml:space="preserve">Look-alike domain already observed in the exercise. Evidence: E6</t>
         </r>
       </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>1</xdr:col>
+                <xdr:colOff>35</xdr:colOff>
+                <xdr:row>0</xdr:row>
+                <xdr:rowOff>2</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>2</xdr:col>
+                <xdr:colOff>-265</xdr:colOff>
+                <xdr:row>3</xdr:row>
+                <xdr:rowOff>7</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
     </comment>
     <comment ref="D4" authorId="0">
       <text>
@@ -410,6 +1040,27 @@
           <t xml:space="preserve">Push MFA is bypassable by fatigue; no conditional access or macro blocking evidenced. Evidence: E6</t>
         </r>
       </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>1</xdr:col>
+                <xdr:colOff>35</xdr:colOff>
+                <xdr:row>0</xdr:row>
+                <xdr:rowOff>2</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>2</xdr:col>
+                <xdr:colOff>-265</xdr:colOff>
+                <xdr:row>3</xdr:row>
+                <xdr:rowOff>25</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
     </comment>
     <comment ref="D5" authorId="0">
       <text>
@@ -422,6 +1073,27 @@
           <t xml:space="preserve">Multiple weak links (triage, segmentation, backup isolation) but perimeter controls exist. Evidence: E2, E6</t>
         </r>
       </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>1</xdr:col>
+                <xdr:colOff>35</xdr:colOff>
+                <xdr:row>0</xdr:row>
+                <xdr:rowOff>2</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>2</xdr:col>
+                <xdr:colOff>-265</xdr:colOff>
+                <xdr:row>3</xdr:row>
+                <xdr:rowOff>25</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
     </comment>
     <comment ref="D6" authorId="0">
       <text>
@@ -434,6 +1106,27 @@
           <t xml:space="preserve">Isolation unknown; failures in E6 suggest exposure. Evidence: E2, E6</t>
         </r>
       </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>1</xdr:col>
+                <xdr:colOff>35</xdr:colOff>
+                <xdr:row>0</xdr:row>
+                <xdr:rowOff>2</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>2</xdr:col>
+                <xdr:colOff>-265</xdr:colOff>
+                <xdr:row>3</xdr:row>
+                <xdr:rowOff>7</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
     </comment>
     <comment ref="D7" authorId="0">
       <text>
@@ -446,6 +1139,27 @@
           <t xml:space="preserve">Depends on sharing configuration - unknown; E6 suggests weakness. Evidence: E6</t>
         </r>
       </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>1</xdr:col>
+                <xdr:colOff>35</xdr:colOff>
+                <xdr:row>0</xdr:row>
+                <xdr:rowOff>2</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>2</xdr:col>
+                <xdr:colOff>-265</xdr:colOff>
+                <xdr:row>3</xdr:row>
+                <xdr:rowOff>10</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
     </comment>
     <comment ref="D8" authorId="0">
       <text>
@@ -458,6 +1172,27 @@
           <t xml:space="preserve">Legitimate access bypasses perimeter controls; no analytics. Evidence: E6, E7</t>
         </r>
       </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>1</xdr:col>
+                <xdr:colOff>35</xdr:colOff>
+                <xdr:row>0</xdr:row>
+                <xdr:rowOff>2</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>2</xdr:col>
+                <xdr:colOff>-265</xdr:colOff>
+                <xdr:row>3</xdr:row>
+                <xdr:rowOff>7</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
     </comment>
     <comment ref="D9" authorId="0">
       <text>
@@ -470,6 +1205,27 @@
           <t xml:space="preserve">Patching lag documented; inventory incomplete. Evidence: E3, E7</t>
         </r>
       </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>1</xdr:col>
+                <xdr:colOff>35</xdr:colOff>
+                <xdr:row>0</xdr:row>
+                <xdr:rowOff>2</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>2</xdr:col>
+                <xdr:colOff>-265</xdr:colOff>
+                <xdr:row>3</xdr:row>
+                <xdr:rowOff>7</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
     </comment>
     <comment ref="D10" authorId="0">
       <text>
@@ -482,6 +1238,27 @@
           <t xml:space="preserve">Patch and segmentation constraints documented. Evidence: E3, E4</t>
         </r>
       </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>1</xdr:col>
+                <xdr:colOff>35</xdr:colOff>
+                <xdr:row>0</xdr:row>
+                <xdr:rowOff>2</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>2</xdr:col>
+                <xdr:colOff>-265</xdr:colOff>
+                <xdr:row>3</xdr:row>
+                <xdr:rowOff>10</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
     </comment>
     <comment ref="D11" authorId="0">
       <text>
@@ -494,6 +1271,27 @@
           <t xml:space="preserve">Evidence of mis-triaged alerts and uncorrelated signals. Evidence: E6</t>
         </r>
       </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>1</xdr:col>
+                <xdr:colOff>35</xdr:colOff>
+                <xdr:row>0</xdr:row>
+                <xdr:rowOff>2</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>2</xdr:col>
+                <xdr:colOff>-265</xdr:colOff>
+                <xdr:row>3</xdr:row>
+                <xdr:rowOff>7</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
     </comment>
     <comment ref="D12" authorId="0">
       <text>
@@ -506,6 +1304,27 @@
           <t xml:space="preserve">Controls over vendor access not evidenced. Evidence: E7</t>
         </r>
       </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>1</xdr:col>
+                <xdr:colOff>35</xdr:colOff>
+                <xdr:row>0</xdr:row>
+                <xdr:rowOff>2</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>2</xdr:col>
+                <xdr:colOff>-265</xdr:colOff>
+                <xdr:row>3</xdr:row>
+                <xdr:rowOff>7</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
     </comment>
     <comment ref="D13" authorId="0">
       <text>
@@ -518,6 +1337,27 @@
           <t xml:space="preserve">Requires write access; monitoring absent. Evidence: E8</t>
         </r>
       </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>1</xdr:col>
+                <xdr:colOff>35</xdr:colOff>
+                <xdr:row>0</xdr:row>
+                <xdr:rowOff>2</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>2</xdr:col>
+                <xdr:colOff>-265</xdr:colOff>
+                <xdr:row>3</xdr:row>
+                <xdr:rowOff>7</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
     </comment>
     <comment ref="D14" authorId="0">
       <text>
@@ -530,6 +1370,27 @@
           <t xml:space="preserve">No vault, scanning or rotation evidenced. Evidence: E7</t>
         </r>
       </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>1</xdr:col>
+                <xdr:colOff>35</xdr:colOff>
+                <xdr:row>0</xdr:row>
+                <xdr:rowOff>2</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>2</xdr:col>
+                <xdr:colOff>-265</xdr:colOff>
+                <xdr:row>3</xdr:row>
+                <xdr:rowOff>7</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
     </comment>
     <comment ref="D15" authorId="0">
       <text>
@@ -542,6 +1403,27 @@
           <t xml:space="preserve">Wireless controls unknown. Evidence: E7</t>
         </r>
       </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>1</xdr:col>
+                <xdr:colOff>35</xdr:colOff>
+                <xdr:row>0</xdr:row>
+                <xdr:rowOff>2</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>2</xdr:col>
+                <xdr:colOff>-265</xdr:colOff>
+                <xdr:row>3</xdr:row>
+                <xdr:rowOff>7</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
     </comment>
     <comment ref="D16" authorId="0">
       <text>
@@ -554,6 +1436,27 @@
           <t xml:space="preserve">No mitigation evidenced. Evidence: E2</t>
         </r>
       </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>1</xdr:col>
+                <xdr:colOff>35</xdr:colOff>
+                <xdr:row>0</xdr:row>
+                <xdr:rowOff>2</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>2</xdr:col>
+                <xdr:colOff>-265</xdr:colOff>
+                <xdr:row>3</xdr:row>
+                <xdr:rowOff>7</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
     </comment>
     <comment ref="D17" authorId="0">
       <text>
@@ -566,6 +1469,27 @@
           <t xml:space="preserve">Verification procedures unknown. Evidence: E1</t>
         </r>
       </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>1</xdr:col>
+                <xdr:colOff>35</xdr:colOff>
+                <xdr:row>0</xdr:row>
+                <xdr:rowOff>2</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>2</xdr:col>
+                <xdr:colOff>-265</xdr:colOff>
+                <xdr:row>3</xdr:row>
+                <xdr:rowOff>7</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
     </comment>
     <comment ref="D18" authorId="0">
       <text>
@@ -578,6 +1502,27 @@
           <t xml:space="preserve">Some protection may exist but is not evidenced. Evidence: E2</t>
         </r>
       </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>1</xdr:col>
+                <xdr:colOff>35</xdr:colOff>
+                <xdr:row>0</xdr:row>
+                <xdr:rowOff>2</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>2</xdr:col>
+                <xdr:colOff>-265</xdr:colOff>
+                <xdr:row>3</xdr:row>
+                <xdr:rowOff>7</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
     </comment>
     <comment ref="D19" authorId="0">
       <text>
@@ -590,6 +1535,27 @@
           <t xml:space="preserve">Redundancy not evidenced. Evidence: E2</t>
         </r>
       </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>1</xdr:col>
+                <xdr:colOff>35</xdr:colOff>
+                <xdr:row>0</xdr:row>
+                <xdr:rowOff>2</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>2</xdr:col>
+                <xdr:colOff>-265</xdr:colOff>
+                <xdr:row>3</xdr:row>
+                <xdr:rowOff>7</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
     </comment>
     <comment ref="D20" authorId="0">
       <text>
@@ -602,6 +1568,27 @@
           <t xml:space="preserve">Access controls and inventory unknown. Evidence: E4</t>
         </r>
       </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>1</xdr:col>
+                <xdr:colOff>35</xdr:colOff>
+                <xdr:row>0</xdr:row>
+                <xdr:rowOff>2</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>2</xdr:col>
+                <xdr:colOff>-265</xdr:colOff>
+                <xdr:row>3</xdr:row>
+                <xdr:rowOff>7</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
     </comment>
     <comment ref="D21" authorId="0">
       <text>
@@ -614,6 +1601,27 @@
           <t xml:space="preserve">Flaw presence unknown; no testing evidence. Evidence: E7</t>
         </r>
       </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>1</xdr:col>
+                <xdr:colOff>35</xdr:colOff>
+                <xdr:row>0</xdr:row>
+                <xdr:rowOff>2</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>2</xdr:col>
+                <xdr:colOff>-265</xdr:colOff>
+                <xdr:row>3</xdr:row>
+                <xdr:rowOff>7</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
     </comment>
     <comment ref="D22" authorId="0">
       <text>
@@ -626,6 +1634,27 @@
           <t xml:space="preserve">Signed updates bypass most customer controls. Evidence: E7</t>
         </r>
       </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>1</xdr:col>
+                <xdr:colOff>35</xdr:colOff>
+                <xdr:row>0</xdr:row>
+                <xdr:rowOff>2</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>2</xdr:col>
+                <xdr:colOff>-265</xdr:colOff>
+                <xdr:row>3</xdr:row>
+                <xdr:rowOff>7</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
     </comment>
     <comment ref="D23" authorId="0">
       <text>
@@ -638,6 +1667,27 @@
           <t xml:space="preserve">Push MFA and no conditional access. Evidence: E6</t>
         </r>
       </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>1</xdr:col>
+                <xdr:colOff>35</xdr:colOff>
+                <xdr:row>0</xdr:row>
+                <xdr:rowOff>2</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>2</xdr:col>
+                <xdr:colOff>-265</xdr:colOff>
+                <xdr:row>3</xdr:row>
+                <xdr:rowOff>7</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
     </comment>
     <comment ref="D24" authorId="0">
       <text>
@@ -650,6 +1700,27 @@
           <t xml:space="preserve">Few technical safeguards evidenced. Evidence: E7</t>
         </r>
       </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>1</xdr:col>
+                <xdr:colOff>35</xdr:colOff>
+                <xdr:row>0</xdr:row>
+                <xdr:rowOff>2</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>2</xdr:col>
+                <xdr:colOff>-265</xdr:colOff>
+                <xdr:row>3</xdr:row>
+                <xdr:rowOff>7</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
     </comment>
     <comment ref="D25" authorId="0">
       <text>
@@ -662,6 +1733,27 @@
           <t xml:space="preserve">Configuration unknown. Evidence: E2</t>
         </r>
       </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>1</xdr:col>
+                <xdr:colOff>35</xdr:colOff>
+                <xdr:row>0</xdr:row>
+                <xdr:rowOff>2</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>2</xdr:col>
+                <xdr:colOff>-265</xdr:colOff>
+                <xdr:row>3</xdr:row>
+                <xdr:rowOff>7</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
     </comment>
     <comment ref="D26" authorId="0">
       <text>
@@ -674,6 +1766,27 @@
           <t xml:space="preserve">Depends on actual exposure - unknown. Evidence: E4</t>
         </r>
       </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>1</xdr:col>
+                <xdr:colOff>35</xdr:colOff>
+                <xdr:row>0</xdr:row>
+                <xdr:rowOff>2</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>2</xdr:col>
+                <xdr:colOff>-265</xdr:colOff>
+                <xdr:row>3</xdr:row>
+                <xdr:rowOff>7</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
     </comment>
     <comment ref="D27" authorId="0">
       <text>
@@ -686,6 +1799,27 @@
           <t xml:space="preserve">Endpoint coverage of device consoles unknown. Evidence: E4</t>
         </r>
       </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>1</xdr:col>
+                <xdr:colOff>35</xdr:colOff>
+                <xdr:row>0</xdr:row>
+                <xdr:rowOff>2</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>2</xdr:col>
+                <xdr:colOff>-265</xdr:colOff>
+                <xdr:row>3</xdr:row>
+                <xdr:rowOff>7</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
     </comment>
     <comment ref="D28" authorId="0">
       <text>
@@ -698,6 +1832,27 @@
           <t xml:space="preserve">Sanitization practice unknown. Evidence: E2</t>
         </r>
       </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>1</xdr:col>
+                <xdr:colOff>35</xdr:colOff>
+                <xdr:row>0</xdr:row>
+                <xdr:rowOff>2</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>2</xdr:col>
+                <xdr:colOff>-265</xdr:colOff>
+                <xdr:row>3</xdr:row>
+                <xdr:rowOff>7</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
     </comment>
     <comment ref="D29" authorId="0">
       <text>
@@ -710,6 +1865,27 @@
           <t xml:space="preserve">No policy or technical controls evidenced. Evidence: E5</t>
         </r>
       </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>1</xdr:col>
+                <xdr:colOff>35</xdr:colOff>
+                <xdr:row>0</xdr:row>
+                <xdr:rowOff>2</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>2</xdr:col>
+                <xdr:colOff>-265</xdr:colOff>
+                <xdr:row>3</xdr:row>
+                <xdr:rowOff>7</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
     </comment>
     <comment ref="D30" authorId="0">
       <text>
@@ -722,6 +1898,27 @@
           <t xml:space="preserve">Verification procedures unknown. Evidence: E3</t>
         </r>
       </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>1</xdr:col>
+                <xdr:colOff>35</xdr:colOff>
+                <xdr:row>0</xdr:row>
+                <xdr:rowOff>2</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>2</xdr:col>
+                <xdr:colOff>-265</xdr:colOff>
+                <xdr:row>3</xdr:row>
+                <xdr:rowOff>7</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
     </comment>
     <comment ref="D31" authorId="0">
       <text>
@@ -734,6 +1931,27 @@
           <t xml:space="preserve">If motivated, broad privileges make success likely. Evidence: E3, E7</t>
         </r>
       </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>1</xdr:col>
+                <xdr:colOff>35</xdr:colOff>
+                <xdr:row>0</xdr:row>
+                <xdr:rowOff>2</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>2</xdr:col>
+                <xdr:colOff>-265</xdr:colOff>
+                <xdr:row>3</xdr:row>
+                <xdr:rowOff>7</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
     </comment>
     <comment ref="D32" authorId="0">
       <text>
@@ -746,6 +1964,27 @@
           <t xml:space="preserve">Cleartext likely; exploitation requires skill. Evidence: E2</t>
         </r>
       </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>1</xdr:col>
+                <xdr:colOff>35</xdr:colOff>
+                <xdr:row>0</xdr:row>
+                <xdr:rowOff>2</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>2</xdr:col>
+                <xdr:colOff>-265</xdr:colOff>
+                <xdr:row>3</xdr:row>
+                <xdr:rowOff>7</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
     </comment>
     <comment ref="D33" authorId="0">
       <text>
@@ -758,6 +1997,27 @@
           <t xml:space="preserve">No brand protection evidenced. Evidence: E6</t>
         </r>
       </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>1</xdr:col>
+                <xdr:colOff>35</xdr:colOff>
+                <xdr:row>0</xdr:row>
+                <xdr:rowOff>2</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>2</xdr:col>
+                <xdr:colOff>-265</xdr:colOff>
+                <xdr:row>3</xdr:row>
+                <xdr:rowOff>7</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
     </comment>
     <comment ref="E4" authorId="0">
       <text>
@@ -770,6 +2030,27 @@
           <t xml:space="preserve">Access to a subset of records; containment possible if detected. Evidence: E1, E6</t>
         </r>
       </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>1</xdr:col>
+                <xdr:colOff>35</xdr:colOff>
+                <xdr:row>0</xdr:row>
+                <xdr:rowOff>2</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>2</xdr:col>
+                <xdr:colOff>-265</xdr:colOff>
+                <xdr:row>3</xdr:row>
+                <xdr:rowOff>7</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
     </comment>
     <comment ref="E5" authorId="0">
       <text>
@@ -782,6 +2063,27 @@
           <t xml:space="preserve">Multi-day disruption of several clinics. Evidence: E1, E6</t>
         </r>
       </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>1</xdr:col>
+                <xdr:colOff>35</xdr:colOff>
+                <xdr:row>0</xdr:row>
+                <xdr:rowOff>2</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>2</xdr:col>
+                <xdr:colOff>-265</xdr:colOff>
+                <xdr:row>3</xdr:row>
+                <xdr:rowOff>7</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
     </comment>
     <comment ref="E6" authorId="0">
       <text>
@@ -794,6 +2096,27 @@
           <t xml:space="preserve">Partial loss of recent restore points. Evidence: E2</t>
         </r>
       </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>1</xdr:col>
+                <xdr:colOff>35</xdr:colOff>
+                <xdr:row>0</xdr:row>
+                <xdr:rowOff>2</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>2</xdr:col>
+                <xdr:colOff>-265</xdr:colOff>
+                <xdr:row>3</xdr:row>
+                <xdr:rowOff>7</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
     </comment>
     <comment ref="E7" authorId="0">
       <text>
@@ -806,6 +2129,27 @@
           <t xml:space="preserve">Partial data set exposed. Evidence: E6</t>
         </r>
       </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>1</xdr:col>
+                <xdr:colOff>35</xdr:colOff>
+                <xdr:row>0</xdr:row>
+                <xdr:rowOff>2</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>2</xdr:col>
+                <xdr:colOff>-265</xdr:colOff>
+                <xdr:row>3</xdr:row>
+                <xdr:rowOff>7</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
     </comment>
     <comment ref="E8" authorId="0">
       <text>
@@ -818,6 +2162,27 @@
           <t xml:space="preserve">Limited set of records. Evidence: E1</t>
         </r>
       </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>1</xdr:col>
+                <xdr:colOff>35</xdr:colOff>
+                <xdr:row>0</xdr:row>
+                <xdr:rowOff>2</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>2</xdr:col>
+                <xdr:colOff>-265</xdr:colOff>
+                <xdr:row>3</xdr:row>
+                <xdr:rowOff>7</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
     </comment>
     <comment ref="E9" authorId="0">
       <text>
@@ -830,6 +2195,27 @@
           <t xml:space="preserve">Foothold with some data access. Evidence: E2</t>
         </r>
       </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>1</xdr:col>
+                <xdr:colOff>35</xdr:colOff>
+                <xdr:row>0</xdr:row>
+                <xdr:rowOff>2</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>2</xdr:col>
+                <xdr:colOff>-265</xdr:colOff>
+                <xdr:row>3</xdr:row>
+                <xdr:rowOff>7</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
     </comment>
     <comment ref="E10" authorId="0">
       <text>
@@ -842,6 +2228,27 @@
           <t xml:space="preserve">Some devices unavailable at one clinic. Evidence: E1</t>
         </r>
       </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>1</xdr:col>
+                <xdr:colOff>35</xdr:colOff>
+                <xdr:row>0</xdr:row>
+                <xdr:rowOff>2</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>2</xdr:col>
+                <xdr:colOff>-265</xdr:colOff>
+                <xdr:row>3</xdr:row>
+                <xdr:rowOff>7</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
     </comment>
     <comment ref="E11" authorId="0">
       <text>
@@ -854,6 +2261,27 @@
           <t xml:space="preserve">Incident escalates before containment. Evidence: E6</t>
         </r>
       </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>1</xdr:col>
+                <xdr:colOff>35</xdr:colOff>
+                <xdr:row>0</xdr:row>
+                <xdr:rowOff>2</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>2</xdr:col>
+                <xdr:colOff>-265</xdr:colOff>
+                <xdr:row>3</xdr:row>
+                <xdr:rowOff>7</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
     </comment>
     <comment ref="E12" authorId="0">
       <text>
@@ -866,6 +2294,27 @@
           <t xml:space="preserve">Breach through one vendor path. Evidence: E2</t>
         </r>
       </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>1</xdr:col>
+                <xdr:colOff>35</xdr:colOff>
+                <xdr:row>0</xdr:row>
+                <xdr:rowOff>2</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>2</xdr:col>
+                <xdr:colOff>-265</xdr:colOff>
+                <xdr:row>3</xdr:row>
+                <xdr:rowOff>7</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
     </comment>
     <comment ref="E13" authorId="0">
       <text>
@@ -878,6 +2327,27 @@
           <t xml:space="preserve">Limited record set altered and detected. Evidence: E1</t>
         </r>
       </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>1</xdr:col>
+                <xdr:colOff>35</xdr:colOff>
+                <xdr:row>0</xdr:row>
+                <xdr:rowOff>2</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>2</xdr:col>
+                <xdr:colOff>-265</xdr:colOff>
+                <xdr:row>3</xdr:row>
+                <xdr:rowOff>7</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
     </comment>
     <comment ref="E14" authorId="0">
       <text>
@@ -890,6 +2360,27 @@
           <t xml:space="preserve">Data reachable by one key. Evidence: E7</t>
         </r>
       </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>1</xdr:col>
+                <xdr:colOff>35</xdr:colOff>
+                <xdr:row>0</xdr:row>
+                <xdr:rowOff>2</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>2</xdr:col>
+                <xdr:colOff>-265</xdr:colOff>
+                <xdr:row>3</xdr:row>
+                <xdr:rowOff>7</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
     </comment>
     <comment ref="E15" authorId="0">
       <text>
@@ -902,6 +2393,27 @@
           <t xml:space="preserve">Access limited to one clinic. Evidence: E1</t>
         </r>
       </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>1</xdr:col>
+                <xdr:colOff>35</xdr:colOff>
+                <xdr:row>0</xdr:row>
+                <xdr:rowOff>2</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>2</xdr:col>
+                <xdr:colOff>-265</xdr:colOff>
+                <xdr:row>3</xdr:row>
+                <xdr:rowOff>7</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
     </comment>
     <comment ref="E16" authorId="0">
       <text>
@@ -914,6 +2426,27 @@
           <t xml:space="preserve">Hours of online unavailability. Evidence: E8</t>
         </r>
       </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>1</xdr:col>
+                <xdr:colOff>35</xdr:colOff>
+                <xdr:row>0</xdr:row>
+                <xdr:rowOff>2</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>2</xdr:col>
+                <xdr:colOff>-265</xdr:colOff>
+                <xdr:row>3</xdr:row>
+                <xdr:rowOff>7</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
     </comment>
     <comment ref="E17" authorId="0">
       <text>
@@ -926,6 +2459,27 @@
           <t xml:space="preserve">One diverted payment. Evidence: E1</t>
         </r>
       </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>1</xdr:col>
+                <xdr:colOff>35</xdr:colOff>
+                <xdr:row>0</xdr:row>
+                <xdr:rowOff>2</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>2</xdr:col>
+                <xdr:colOff>-265</xdr:colOff>
+                <xdr:row>3</xdr:row>
+                <xdr:rowOff>7</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
     </comment>
     <comment ref="E18" authorId="0">
       <text>
@@ -938,6 +2492,27 @@
           <t xml:space="preserve">Small number of records. Evidence: E2</t>
         </r>
       </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>1</xdr:col>
+                <xdr:colOff>35</xdr:colOff>
+                <xdr:row>0</xdr:row>
+                <xdr:rowOff>2</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>2</xdr:col>
+                <xdr:colOff>-265</xdr:colOff>
+                <xdr:row>3</xdr:row>
+                <xdr:rowOff>7</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
     </comment>
     <comment ref="E19" authorId="0">
       <text>
@@ -950,6 +2525,27 @@
           <t xml:space="preserve">Hours of network-wide outage. Evidence: E1</t>
         </r>
       </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>1</xdr:col>
+                <xdr:colOff>35</xdr:colOff>
+                <xdr:row>0</xdr:row>
+                <xdr:rowOff>2</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>2</xdr:col>
+                <xdr:colOff>-265</xdr:colOff>
+                <xdr:row>3</xdr:row>
+                <xdr:rowOff>7</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
     </comment>
     <comment ref="E20" authorId="0">
       <text>
@@ -962,6 +2558,27 @@
           <t xml:space="preserve">One clinic's local data. Evidence: E2</t>
         </r>
       </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>1</xdr:col>
+                <xdr:colOff>35</xdr:colOff>
+                <xdr:row>0</xdr:row>
+                <xdr:rowOff>2</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>2</xdr:col>
+                <xdr:colOff>-265</xdr:colOff>
+                <xdr:row>3</xdr:row>
+                <xdr:rowOff>7</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
     </comment>
     <comment ref="E21" authorId="0">
       <text>
@@ -974,6 +2591,27 @@
           <t xml:space="preserve">Partial enumeration before detection. Evidence: E8</t>
         </r>
       </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>1</xdr:col>
+                <xdr:colOff>35</xdr:colOff>
+                <xdr:row>0</xdr:row>
+                <xdr:rowOff>2</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>2</xdr:col>
+                <xdr:colOff>-265</xdr:colOff>
+                <xdr:row>3</xdr:row>
+                <xdr:rowOff>7</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
     </comment>
     <comment ref="E22" authorId="0">
       <text>
@@ -986,6 +2624,27 @@
           <t xml:space="preserve">Foothold on many hosts. Evidence: E2</t>
         </r>
       </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>1</xdr:col>
+                <xdr:colOff>35</xdr:colOff>
+                <xdr:row>0</xdr:row>
+                <xdr:rowOff>2</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>2</xdr:col>
+                <xdr:colOff>-265</xdr:colOff>
+                <xdr:row>3</xdr:row>
+                <xdr:rowOff>7</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
     </comment>
     <comment ref="E23" authorId="0">
       <text>
@@ -998,6 +2657,27 @@
           <t xml:space="preserve">Partial tenant data access. Evidence: E2</t>
         </r>
       </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>1</xdr:col>
+                <xdr:colOff>35</xdr:colOff>
+                <xdr:row>0</xdr:row>
+                <xdr:rowOff>2</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>2</xdr:col>
+                <xdr:colOff>-265</xdr:colOff>
+                <xdr:row>3</xdr:row>
+                <xdr:rowOff>7</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
     </comment>
     <comment ref="E24" authorId="0">
       <text>
@@ -1010,6 +2690,27 @@
           <t xml:space="preserve">Single patient or small batch. Evidence: E1</t>
         </r>
       </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>1</xdr:col>
+                <xdr:colOff>35</xdr:colOff>
+                <xdr:row>0</xdr:row>
+                <xdr:rowOff>2</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>2</xdr:col>
+                <xdr:colOff>-265</xdr:colOff>
+                <xdr:row>3</xdr:row>
+                <xdr:rowOff>7</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
     </comment>
     <comment ref="E25" authorId="0">
       <text>
@@ -1022,6 +2723,27 @@
           <t xml:space="preserve">Individual consultations. Evidence: E2</t>
         </r>
       </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>1</xdr:col>
+                <xdr:colOff>35</xdr:colOff>
+                <xdr:row>0</xdr:row>
+                <xdr:rowOff>2</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>2</xdr:col>
+                <xdr:colOff>-265</xdr:colOff>
+                <xdr:row>3</xdr:row>
+                <xdr:rowOff>7</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
     </comment>
     <comment ref="E26" authorId="0">
       <text>
@@ -1034,6 +2756,27 @@
           <t xml:space="preserve">Control of one infrastructure component. Evidence: E2</t>
         </r>
       </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>1</xdr:col>
+                <xdr:colOff>35</xdr:colOff>
+                <xdr:row>0</xdr:row>
+                <xdr:rowOff>2</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>2</xdr:col>
+                <xdr:colOff>-265</xdr:colOff>
+                <xdr:row>3</xdr:row>
+                <xdr:rowOff>7</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
     </comment>
     <comment ref="E27" authorId="0">
       <text>
@@ -1046,6 +2789,27 @@
           <t xml:space="preserve">One imaging area disrupted. Evidence: E2</t>
         </r>
       </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>1</xdr:col>
+                <xdr:colOff>35</xdr:colOff>
+                <xdr:row>0</xdr:row>
+                <xdr:rowOff>2</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>2</xdr:col>
+                <xdr:colOff>-265</xdr:colOff>
+                <xdr:row>3</xdr:row>
+                <xdr:rowOff>7</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
     </comment>
     <comment ref="E28" authorId="0">
       <text>
@@ -1058,6 +2822,27 @@
           <t xml:space="preserve">One device's data. Evidence: E2</t>
         </r>
       </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>1</xdr:col>
+                <xdr:colOff>35</xdr:colOff>
+                <xdr:row>0</xdr:row>
+                <xdr:rowOff>2</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>2</xdr:col>
+                <xdr:colOff>-265</xdr:colOff>
+                <xdr:row>3</xdr:row>
+                <xdr:rowOff>7</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
     </comment>
     <comment ref="E29" authorId="0">
       <text>
@@ -1070,6 +2855,27 @@
           <t xml:space="preserve">Limited volume, low misuse likelihood. Evidence: E1</t>
         </r>
       </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>1</xdr:col>
+                <xdr:colOff>35</xdr:colOff>
+                <xdr:row>0</xdr:row>
+                <xdr:rowOff>2</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>2</xdr:col>
+                <xdr:colOff>-265</xdr:colOff>
+                <xdr:row>3</xdr:row>
+                <xdr:rowOff>7</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
     </comment>
     <comment ref="E30" authorId="0">
       <text>
@@ -1082,6 +2888,27 @@
           <t xml:space="preserve">One account's reach. Evidence: E6</t>
         </r>
       </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>1</xdr:col>
+                <xdr:colOff>35</xdr:colOff>
+                <xdr:row>0</xdr:row>
+                <xdr:rowOff>2</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>2</xdr:col>
+                <xdr:colOff>-265</xdr:colOff>
+                <xdr:row>3</xdr:row>
+                <xdr:rowOff>7</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
     </comment>
     <comment ref="E31" authorId="0">
       <text>
@@ -1094,6 +2921,27 @@
           <t xml:space="preserve">Several systems destroyed. Evidence: E2</t>
         </r>
       </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>1</xdr:col>
+                <xdr:colOff>35</xdr:colOff>
+                <xdr:row>0</xdr:row>
+                <xdr:rowOff>2</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>2</xdr:col>
+                <xdr:colOff>-265</xdr:colOff>
+                <xdr:row>3</xdr:row>
+                <xdr:rowOff>7</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
     </comment>
     <comment ref="E32" authorId="0">
       <text>
@@ -1106,6 +2954,27 @@
           <t xml:space="preserve">Some results exposed. Evidence: E2</t>
         </r>
       </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>1</xdr:col>
+                <xdr:colOff>35</xdr:colOff>
+                <xdr:row>0</xdr:row>
+                <xdr:rowOff>2</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>2</xdr:col>
+                <xdr:colOff>-265</xdr:colOff>
+                <xdr:row>3</xdr:row>
+                <xdr:rowOff>7</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
     </comment>
     <comment ref="E33" authorId="0">
       <text>
@@ -1118,6 +2987,27 @@
           <t xml:space="preserve">Some patients defrauded. Evidence: E6</t>
         </r>
       </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>1</xdr:col>
+                <xdr:colOff>35</xdr:colOff>
+                <xdr:row>0</xdr:row>
+                <xdr:rowOff>2</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>2</xdr:col>
+                <xdr:colOff>-265</xdr:colOff>
+                <xdr:row>3</xdr:row>
+                <xdr:rowOff>7</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
     </comment>
     <comment ref="F4" authorId="0">
       <text>
@@ -1130,6 +3020,27 @@
           <t xml:space="preserve">Full EHR access or pivot to ransomware. Evidence: E1</t>
         </r>
       </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>1</xdr:col>
+                <xdr:colOff>35</xdr:colOff>
+                <xdr:row>0</xdr:row>
+                <xdr:rowOff>2</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>2</xdr:col>
+                <xdr:colOff>-265</xdr:colOff>
+                <xdr:row>3</xdr:row>
+                <xdr:rowOff>7</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
     </comment>
     <comment ref="F5" authorId="0">
       <text>
@@ -1142,6 +3053,27 @@
           <t xml:space="preserve">Network-wide outage with data theft and failed recovery. Evidence: E1</t>
         </r>
       </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>1</xdr:col>
+                <xdr:colOff>35</xdr:colOff>
+                <xdr:row>0</xdr:row>
+                <xdr:rowOff>2</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>2</xdr:col>
+                <xdr:colOff>-265</xdr:colOff>
+                <xdr:row>3</xdr:row>
+                <xdr:rowOff>7</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
     </comment>
     <comment ref="F6" authorId="0">
       <text>
@@ -1154,6 +3086,27 @@
           <t xml:space="preserve">No usable backup for EHR. Evidence: E1</t>
         </r>
       </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>1</xdr:col>
+                <xdr:colOff>35</xdr:colOff>
+                <xdr:row>0</xdr:row>
+                <xdr:rowOff>2</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>2</xdr:col>
+                <xdr:colOff>-265</xdr:colOff>
+                <xdr:row>3</xdr:row>
+                <xdr:rowOff>7</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
     </comment>
     <comment ref="F7" authorId="0">
       <text>
@@ -1166,6 +3119,27 @@
           <t xml:space="preserve">Entire export history exposed. Evidence: E1</t>
         </r>
       </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>1</xdr:col>
+                <xdr:colOff>35</xdr:colOff>
+                <xdr:row>0</xdr:row>
+                <xdr:rowOff>2</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>2</xdr:col>
+                <xdr:colOff>-265</xdr:colOff>
+                <xdr:row>3</xdr:row>
+                <xdr:rowOff>7</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
     </comment>
     <comment ref="F8" authorId="0">
       <text>
@@ -1178,6 +3152,27 @@
           <t xml:space="preserve">Bulk extraction through the service account. Evidence: E6</t>
         </r>
       </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>1</xdr:col>
+                <xdr:colOff>35</xdr:colOff>
+                <xdr:row>0</xdr:row>
+                <xdr:rowOff>2</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>2</xdr:col>
+                <xdr:colOff>-265</xdr:colOff>
+                <xdr:row>3</xdr:row>
+                <xdr:rowOff>7</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
     </comment>
     <comment ref="F9" authorId="0">
       <text>
@@ -1190,6 +3185,27 @@
           <t xml:space="preserve">Precursor to network-wide ransomware. Evidence: E1</t>
         </r>
       </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>1</xdr:col>
+                <xdr:colOff>35</xdr:colOff>
+                <xdr:row>0</xdr:row>
+                <xdr:rowOff>2</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>2</xdr:col>
+                <xdr:colOff>-265</xdr:colOff>
+                <xdr:row>3</xdr:row>
+                <xdr:rowOff>7</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
     </comment>
     <comment ref="F10" authorId="0">
       <text>
@@ -1202,6 +3218,27 @@
           <t xml:space="preserve">Patient harm from altered or unavailable equipment. Evidence: E5</t>
         </r>
       </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>1</xdr:col>
+                <xdr:colOff>35</xdr:colOff>
+                <xdr:row>0</xdr:row>
+                <xdr:rowOff>2</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>2</xdr:col>
+                <xdr:colOff>-265</xdr:colOff>
+                <xdr:row>3</xdr:row>
+                <xdr:rowOff>7</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
     </comment>
     <comment ref="F11" authorId="0">
       <text>
@@ -1214,6 +3251,27 @@
           <t xml:space="preserve">Full ransomware and breach scenario. Evidence: E6</t>
         </r>
       </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>1</xdr:col>
+                <xdr:colOff>35</xdr:colOff>
+                <xdr:row>0</xdr:row>
+                <xdr:rowOff>2</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>2</xdr:col>
+                <xdr:colOff>-265</xdr:colOff>
+                <xdr:row>3</xdr:row>
+                <xdr:rowOff>7</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
     </comment>
     <comment ref="F12" authorId="0">
       <text>
@@ -1226,6 +3284,27 @@
           <t xml:space="preserve">EHR vendor compromise affecting all clinics. Evidence: E1</t>
         </r>
       </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>1</xdr:col>
+                <xdr:colOff>35</xdr:colOff>
+                <xdr:row>0</xdr:row>
+                <xdr:rowOff>2</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>2</xdr:col>
+                <xdr:colOff>-265</xdr:colOff>
+                <xdr:row>3</xdr:row>
+                <xdr:rowOff>7</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
     </comment>
     <comment ref="F13" authorId="0">
       <text>
@@ -1238,6 +3317,27 @@
           <t xml:space="preserve">Patient harm from undetected alteration. Evidence: E5</t>
         </r>
       </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>1</xdr:col>
+                <xdr:colOff>35</xdr:colOff>
+                <xdr:row>0</xdr:row>
+                <xdr:rowOff>2</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>2</xdr:col>
+                <xdr:colOff>-265</xdr:colOff>
+                <xdr:row>3</xdr:row>
+                <xdr:rowOff>7</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
     </comment>
     <comment ref="F14" authorId="0">
       <text>
@@ -1250,6 +3350,27 @@
           <t xml:space="preserve">Key with broad EHR or storage scope. Evidence: E1</t>
         </r>
       </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>1</xdr:col>
+                <xdr:colOff>35</xdr:colOff>
+                <xdr:row>0</xdr:row>
+                <xdr:rowOff>2</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>2</xdr:col>
+                <xdr:colOff>-265</xdr:colOff>
+                <xdr:row>3</xdr:row>
+                <xdr:rowOff>7</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
     </comment>
     <comment ref="F15" authorId="0">
       <text>
@@ -1262,6 +3383,27 @@
           <t xml:space="preserve">Foothold leading to network-wide compromise. Evidence: E2</t>
         </r>
       </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>1</xdr:col>
+                <xdr:colOff>35</xdr:colOff>
+                <xdr:row>0</xdr:row>
+                <xdr:rowOff>2</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>2</xdr:col>
+                <xdr:colOff>-265</xdr:colOff>
+                <xdr:row>3</xdr:row>
+                <xdr:rowOff>7</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
     </comment>
     <comment ref="F16" authorId="0">
       <text>
@@ -1274,6 +3416,27 @@
           <t xml:space="preserve">Multi-day disruption including cloud access. Evidence: E2</t>
         </r>
       </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>1</xdr:col>
+                <xdr:colOff>35</xdr:colOff>
+                <xdr:row>0</xdr:row>
+                <xdr:rowOff>2</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>2</xdr:col>
+                <xdr:colOff>-265</xdr:colOff>
+                <xdr:row>3</xdr:row>
+                <xdr:rowOff>7</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
     </comment>
     <comment ref="F17" authorId="0">
       <text>
@@ -1286,6 +3449,27 @@
           <t xml:space="preserve">Several large payments diverted. Evidence: E3</t>
         </r>
       </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>1</xdr:col>
+                <xdr:colOff>35</xdr:colOff>
+                <xdr:row>0</xdr:row>
+                <xdr:rowOff>2</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>2</xdr:col>
+                <xdr:colOff>-265</xdr:colOff>
+                <xdr:row>3</xdr:row>
+                <xdr:rowOff>7</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
     </comment>
     <comment ref="F18" authorId="0">
       <text>
@@ -1298,6 +3482,27 @@
           <t xml:space="preserve">Live EHR session allows wider access. Evidence: E2</t>
         </r>
       </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>1</xdr:col>
+                <xdr:colOff>35</xdr:colOff>
+                <xdr:row>0</xdr:row>
+                <xdr:rowOff>2</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>2</xdr:col>
+                <xdr:colOff>-265</xdr:colOff>
+                <xdr:row>3</xdr:row>
+                <xdr:rowOff>7</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
     </comment>
     <comment ref="F19" authorId="0">
       <text>
@@ -1310,6 +3515,27 @@
           <t xml:space="preserve">Multi-day loss of the hub. Evidence: E2</t>
         </r>
       </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>1</xdr:col>
+                <xdr:colOff>35</xdr:colOff>
+                <xdr:row>0</xdr:row>
+                <xdr:rowOff>2</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>2</xdr:col>
+                <xdr:colOff>-265</xdr:colOff>
+                <xdr:row>3</xdr:row>
+                <xdr:rowOff>7</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
     </comment>
     <comment ref="F20" authorId="0">
       <text>
@@ -1322,6 +3548,27 @@
           <t xml:space="preserve">Multiple clinics' historical data. Evidence: E2</t>
         </r>
       </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>1</xdr:col>
+                <xdr:colOff>35</xdr:colOff>
+                <xdr:row>0</xdr:row>
+                <xdr:rowOff>2</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>2</xdr:col>
+                <xdr:colOff>-265</xdr:colOff>
+                <xdr:row>3</xdr:row>
+                <xdr:rowOff>7</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
     </comment>
     <comment ref="F21" authorId="0">
       <text>
@@ -1334,6 +3581,27 @@
           <t xml:space="preserve">Full patient document store. Evidence: E1</t>
         </r>
       </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>1</xdr:col>
+                <xdr:colOff>35</xdr:colOff>
+                <xdr:row>0</xdr:row>
+                <xdr:rowOff>2</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>2</xdr:col>
+                <xdr:colOff>-265</xdr:colOff>
+                <xdr:row>3</xdr:row>
+                <xdr:rowOff>7</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
     </comment>
     <comment ref="F22" authorId="0">
       <text>
@@ -1346,6 +3614,27 @@
           <t xml:space="preserve">Enterprise-wide compromise. Evidence: E2</t>
         </r>
       </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>1</xdr:col>
+                <xdr:colOff>35</xdr:colOff>
+                <xdr:row>0</xdr:row>
+                <xdr:rowOff>2</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>2</xdr:col>
+                <xdr:colOff>-265</xdr:colOff>
+                <xdr:row>3</xdr:row>
+                <xdr:rowOff>7</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
     </comment>
     <comment ref="F23" authorId="0">
       <text>
@@ -1358,6 +3647,27 @@
           <t xml:space="preserve">Full tenant takeover. Evidence: E2</t>
         </r>
       </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>1</xdr:col>
+                <xdr:colOff>35</xdr:colOff>
+                <xdr:row>0</xdr:row>
+                <xdr:rowOff>2</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>2</xdr:col>
+                <xdr:colOff>-265</xdr:colOff>
+                <xdr:row>3</xdr:row>
+                <xdr:rowOff>7</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
     </comment>
     <comment ref="F24" authorId="0">
       <text>
@@ -1370,6 +3680,27 @@
           <t xml:space="preserve">Large batch sent externally. Evidence: E1</t>
         </r>
       </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>1</xdr:col>
+                <xdr:colOff>35</xdr:colOff>
+                <xdr:row>0</xdr:row>
+                <xdr:rowOff>2</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>2</xdr:col>
+                <xdr:colOff>-265</xdr:colOff>
+                <xdr:row>3</xdr:row>
+                <xdr:rowOff>7</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
     </comment>
     <comment ref="F25" authorId="0">
       <text>
@@ -1382,6 +3713,27 @@
           <t xml:space="preserve">Systematic interception. Evidence: E2</t>
         </r>
       </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>1</xdr:col>
+                <xdr:colOff>35</xdr:colOff>
+                <xdr:row>0</xdr:row>
+                <xdr:rowOff>2</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>2</xdr:col>
+                <xdr:colOff>-265</xdr:colOff>
+                <xdr:row>3</xdr:row>
+                <xdr:rowOff>7</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
     </comment>
     <comment ref="F26" authorId="0">
       <text>
@@ -1394,6 +3746,27 @@
           <t xml:space="preserve">Hypervisor-level ransomware. Evidence: E2</t>
         </r>
       </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>1</xdr:col>
+                <xdr:colOff>35</xdr:colOff>
+                <xdr:row>0</xdr:row>
+                <xdr:rowOff>2</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>2</xdr:col>
+                <xdr:colOff>-265</xdr:colOff>
+                <xdr:row>3</xdr:row>
+                <xdr:rowOff>7</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
     </comment>
     <comment ref="F27" authorId="0">
       <text>
@@ -1406,6 +3779,27 @@
           <t xml:space="preserve">Spread to multiple devices. Evidence: E4</t>
         </r>
       </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>1</xdr:col>
+                <xdr:colOff>35</xdr:colOff>
+                <xdr:row>0</xdr:row>
+                <xdr:rowOff>2</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>2</xdr:col>
+                <xdr:colOff>-265</xdr:colOff>
+                <xdr:row>3</xdr:row>
+                <xdr:rowOff>7</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
     </comment>
     <comment ref="F28" authorId="0">
       <text>
@@ -1418,6 +3812,27 @@
           <t xml:space="preserve">Batch of storage units. Evidence: E2</t>
         </r>
       </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>1</xdr:col>
+                <xdr:colOff>35</xdr:colOff>
+                <xdr:row>0</xdr:row>
+                <xdr:rowOff>2</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>2</xdr:col>
+                <xdr:colOff>-265</xdr:colOff>
+                <xdr:row>3</xdr:row>
+                <xdr:rowOff>7</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
     </comment>
     <comment ref="F29" authorId="0">
       <text>
@@ -1430,6 +3845,27 @@
           <t xml:space="preserve">Systemic transfer plus clinical errors. Evidence: E5</t>
         </r>
       </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>1</xdr:col>
+                <xdr:colOff>35</xdr:colOff>
+                <xdr:row>0</xdr:row>
+                <xdr:rowOff>2</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>2</xdr:col>
+                <xdr:colOff>-265</xdr:colOff>
+                <xdr:row>3</xdr:row>
+                <xdr:rowOff>7</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
     </comment>
     <comment ref="F30" authorId="0">
       <text>
@@ -1442,6 +3878,27 @@
           <t xml:space="preserve">Privileged account leads to enterprise compromise. Evidence: E1</t>
         </r>
       </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>1</xdr:col>
+                <xdr:colOff>35</xdr:colOff>
+                <xdr:row>0</xdr:row>
+                <xdr:rowOff>2</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>2</xdr:col>
+                <xdr:colOff>-265</xdr:colOff>
+                <xdr:row>3</xdr:row>
+                <xdr:rowOff>7</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
     </comment>
     <comment ref="F31" authorId="0">
       <text>
@@ -1454,6 +3911,27 @@
           <t xml:space="preserve">Backups and core systems destroyed. Evidence: E2</t>
         </r>
       </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>1</xdr:col>
+                <xdr:colOff>35</xdr:colOff>
+                <xdr:row>0</xdr:row>
+                <xdr:rowOff>2</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>2</xdr:col>
+                <xdr:colOff>-265</xdr:colOff>
+                <xdr:row>3</xdr:row>
+                <xdr:rowOff>7</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
     </comment>
     <comment ref="F32" authorId="0">
       <text>
@@ -1466,6 +3944,27 @@
           <t xml:space="preserve">Altered results lead to harm. Evidence: E5</t>
         </r>
       </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>1</xdr:col>
+                <xdr:colOff>35</xdr:colOff>
+                <xdr:row>0</xdr:row>
+                <xdr:rowOff>2</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>2</xdr:col>
+                <xdr:colOff>-265</xdr:colOff>
+                <xdr:row>3</xdr:row>
+                <xdr:rowOff>7</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
     </comment>
     <comment ref="F33" authorId="0">
       <text>
@@ -1478,6 +3977,27 @@
           <t xml:space="preserve">Large campaign and portal clone. Evidence: E6</t>
         </r>
       </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>1</xdr:col>
+                <xdr:colOff>35</xdr:colOff>
+                <xdr:row>0</xdr:row>
+                <xdr:rowOff>2</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>2</xdr:col>
+                <xdr:colOff>-265</xdr:colOff>
+                <xdr:row>3</xdr:row>
+                <xdr:rowOff>7</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
     </comment>
     <comment ref="G4" authorId="0">
       <text>
@@ -1490,6 +4010,27 @@
           <t xml:space="preserve">Two-person team; alert triage weak; IR untested. Evidence: E3, E6</t>
         </r>
       </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>1</xdr:col>
+                <xdr:colOff>35</xdr:colOff>
+                <xdr:row>0</xdr:row>
+                <xdr:rowOff>2</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>2</xdr:col>
+                <xdr:colOff>-265</xdr:colOff>
+                <xdr:row>3</xdr:row>
+                <xdr:rowOff>7</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
     </comment>
     <comment ref="G5" authorId="0">
       <text>
@@ -1502,6 +4043,27 @@
           <t xml:space="preserve">Recovery and workarounds untested; small team. Evidence: E3, E7</t>
         </r>
       </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>1</xdr:col>
+                <xdr:colOff>35</xdr:colOff>
+                <xdr:row>0</xdr:row>
+                <xdr:rowOff>2</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>2</xdr:col>
+                <xdr:colOff>-265</xdr:colOff>
+                <xdr:row>3</xdr:row>
+                <xdr:rowOff>7</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
     </comment>
     <comment ref="G6" authorId="0">
       <text>
@@ -1514,6 +4076,27 @@
           <t xml:space="preserve">No restore testing evidence. Evidence: E7</t>
         </r>
       </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>1</xdr:col>
+                <xdr:colOff>35</xdr:colOff>
+                <xdr:row>0</xdr:row>
+                <xdr:rowOff>2</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>2</xdr:col>
+                <xdr:colOff>-265</xdr:colOff>
+                <xdr:row>3</xdr:row>
+                <xdr:rowOff>7</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
     </comment>
     <comment ref="G7" authorId="0">
       <text>
@@ -1526,6 +4109,27 @@
           <t xml:space="preserve">Logging and detection uncertain. Evidence: E4</t>
         </r>
       </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>1</xdr:col>
+                <xdr:colOff>35</xdr:colOff>
+                <xdr:row>0</xdr:row>
+                <xdr:rowOff>2</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>2</xdr:col>
+                <xdr:colOff>-265</xdr:colOff>
+                <xdr:row>3</xdr:row>
+                <xdr:rowOff>7</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
     </comment>
     <comment ref="G8" authorId="0">
       <text>
@@ -1538,6 +4142,27 @@
           <t xml:space="preserve">Logs exist but not monitored. Evidence: E6</t>
         </r>
       </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>1</xdr:col>
+                <xdr:colOff>35</xdr:colOff>
+                <xdr:row>0</xdr:row>
+                <xdr:rowOff>2</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>2</xdr:col>
+                <xdr:colOff>-265</xdr:colOff>
+                <xdr:row>3</xdr:row>
+                <xdr:rowOff>7</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
     </comment>
     <comment ref="G9" authorId="0">
       <text>
@@ -1550,6 +4175,27 @@
           <t xml:space="preserve">Detection of implants uncertain. Evidence: E3</t>
         </r>
       </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>1</xdr:col>
+                <xdr:colOff>35</xdr:colOff>
+                <xdr:row>0</xdr:row>
+                <xdr:rowOff>2</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>2</xdr:col>
+                <xdr:colOff>-265</xdr:colOff>
+                <xdr:row>3</xdr:row>
+                <xdr:rowOff>7</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
     </comment>
     <comment ref="G10" authorId="0">
       <text>
@@ -1562,6 +4208,27 @@
           <t xml:space="preserve">No device monitoring or inventory evidence. Evidence: E4</t>
         </r>
       </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>1</xdr:col>
+                <xdr:colOff>35</xdr:colOff>
+                <xdr:row>0</xdr:row>
+                <xdr:rowOff>2</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>2</xdr:col>
+                <xdr:colOff>-265</xdr:colOff>
+                <xdr:row>3</xdr:row>
+                <xdr:rowOff>7</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
     </comment>
     <comment ref="G11" authorId="0">
       <text>
@@ -1574,6 +4241,27 @@
           <t xml:space="preserve">Detection and response are the weak capability itself. Evidence: E3</t>
         </r>
       </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>1</xdr:col>
+                <xdr:colOff>35</xdr:colOff>
+                <xdr:row>0</xdr:row>
+                <xdr:rowOff>2</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>2</xdr:col>
+                <xdr:colOff>-265</xdr:colOff>
+                <xdr:row>3</xdr:row>
+                <xdr:rowOff>7</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
     </comment>
     <comment ref="G12" authorId="0">
       <text>
@@ -1586,6 +4274,27 @@
           <t xml:space="preserve">Limited visibility into vendor activity. Evidence: E7</t>
         </r>
       </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>1</xdr:col>
+                <xdr:colOff>35</xdr:colOff>
+                <xdr:row>0</xdr:row>
+                <xdr:rowOff>2</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>2</xdr:col>
+                <xdr:colOff>-265</xdr:colOff>
+                <xdr:row>3</xdr:row>
+                <xdr:rowOff>7</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
     </comment>
     <comment ref="G13" authorId="0">
       <text>
@@ -1598,6 +4307,27 @@
           <t xml:space="preserve">Backups exist but integrity verification absent. Evidence: E2</t>
         </r>
       </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>1</xdr:col>
+                <xdr:colOff>35</xdr:colOff>
+                <xdr:row>0</xdr:row>
+                <xdr:rowOff>2</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>2</xdr:col>
+                <xdr:colOff>-265</xdr:colOff>
+                <xdr:row>3</xdr:row>
+                <xdr:rowOff>7</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
     </comment>
     <comment ref="G14" authorId="0">
       <text>
@@ -1610,6 +4340,27 @@
           <t xml:space="preserve">API monitoring not evidenced. Evidence: E7</t>
         </r>
       </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>1</xdr:col>
+                <xdr:colOff>35</xdr:colOff>
+                <xdr:row>0</xdr:row>
+                <xdr:rowOff>2</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>2</xdr:col>
+                <xdr:colOff>-265</xdr:colOff>
+                <xdr:row>3</xdr:row>
+                <xdr:rowOff>7</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
     </comment>
     <comment ref="G15" authorId="0">
       <text>
@@ -1622,6 +4373,27 @@
           <t xml:space="preserve">No clinic-level wireless monitoring evidenced. Evidence: E7</t>
         </r>
       </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>1</xdr:col>
+                <xdr:colOff>35</xdr:colOff>
+                <xdr:row>0</xdr:row>
+                <xdr:rowOff>2</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>2</xdr:col>
+                <xdr:colOff>-265</xdr:colOff>
+                <xdr:row>3</xdr:row>
+                <xdr:rowOff>7</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
     </comment>
     <comment ref="G16" authorId="0">
       <text>
@@ -1634,6 +4406,27 @@
           <t xml:space="preserve">Clinics can operate without online booking. Evidence: E1</t>
         </r>
       </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>1</xdr:col>
+                <xdr:colOff>35</xdr:colOff>
+                <xdr:row>0</xdr:row>
+                <xdr:rowOff>2</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>2</xdr:col>
+                <xdr:colOff>-265</xdr:colOff>
+                <xdr:row>3</xdr:row>
+                <xdr:rowOff>7</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
     </comment>
     <comment ref="G17" authorId="0">
       <text>
@@ -1646,6 +4439,27 @@
           <t xml:space="preserve">Bank recall possible if detected quickly. Evidence: E1</t>
         </r>
       </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>1</xdr:col>
+                <xdr:colOff>35</xdr:colOff>
+                <xdr:row>0</xdr:row>
+                <xdr:rowOff>2</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>2</xdr:col>
+                <xdr:colOff>-265</xdr:colOff>
+                <xdr:row>3</xdr:row>
+                <xdr:rowOff>7</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
     </comment>
     <comment ref="G18" authorId="0">
       <text>
@@ -1658,6 +4472,27 @@
           <t xml:space="preserve">Accounts can be revoked centrally. Evidence: E2</t>
         </r>
       </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>1</xdr:col>
+                <xdr:colOff>35</xdr:colOff>
+                <xdr:row>0</xdr:row>
+                <xdr:rowOff>2</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>2</xdr:col>
+                <xdr:colOff>-265</xdr:colOff>
+                <xdr:row>3</xdr:row>
+                <xdr:rowOff>7</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
     </comment>
     <comment ref="G19" authorId="0">
       <text>
@@ -1670,6 +4505,27 @@
           <t xml:space="preserve">No alternate site or tested downtime procedures. Evidence: E7</t>
         </r>
       </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>1</xdr:col>
+                <xdr:colOff>35</xdr:colOff>
+                <xdr:row>0</xdr:row>
+                <xdr:rowOff>2</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>2</xdr:col>
+                <xdr:colOff>-265</xdr:colOff>
+                <xdr:row>3</xdr:row>
+                <xdr:rowOff>7</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
     </comment>
     <comment ref="G20" authorId="0">
       <text>
@@ -1682,6 +4538,27 @@
           <t xml:space="preserve">No monitoring of local storage. Evidence: E4</t>
         </r>
       </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>1</xdr:col>
+                <xdr:colOff>35</xdr:colOff>
+                <xdr:row>0</xdr:row>
+                <xdr:rowOff>2</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>2</xdr:col>
+                <xdr:colOff>-265</xdr:colOff>
+                <xdr:row>3</xdr:row>
+                <xdr:rowOff>7</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
     </comment>
     <comment ref="G21" authorId="0">
       <text>
@@ -1694,6 +4571,27 @@
           <t xml:space="preserve">Application monitoring unknown. Evidence: E7</t>
         </r>
       </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>1</xdr:col>
+                <xdr:colOff>35</xdr:colOff>
+                <xdr:row>0</xdr:row>
+                <xdr:rowOff>2</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>2</xdr:col>
+                <xdr:colOff>-265</xdr:colOff>
+                <xdr:row>3</xdr:row>
+                <xdr:rowOff>7</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
     </comment>
     <comment ref="G22" authorId="0">
       <text>
@@ -1706,6 +4604,27 @@
           <t xml:space="preserve">Detection depends on external advisories. Evidence: E3</t>
         </r>
       </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>1</xdr:col>
+                <xdr:colOff>35</xdr:colOff>
+                <xdr:row>0</xdr:row>
+                <xdr:rowOff>2</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>2</xdr:col>
+                <xdr:colOff>-265</xdr:colOff>
+                <xdr:row>3</xdr:row>
+                <xdr:rowOff>7</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
     </comment>
     <comment ref="G23" authorId="0">
       <text>
@@ -1718,6 +4637,27 @@
           <t xml:space="preserve">Cloud logging uncertain. Evidence: E4</t>
         </r>
       </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>1</xdr:col>
+                <xdr:colOff>35</xdr:colOff>
+                <xdr:row>0</xdr:row>
+                <xdr:rowOff>2</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>2</xdr:col>
+                <xdr:colOff>-265</xdr:colOff>
+                <xdr:row>3</xdr:row>
+                <xdr:rowOff>7</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
     </comment>
     <comment ref="G24" authorId="0">
       <text>
@@ -1730,6 +4670,27 @@
           <t xml:space="preserve">Privacy function exists to respond. Evidence: E4</t>
         </r>
       </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>1</xdr:col>
+                <xdr:colOff>35</xdr:colOff>
+                <xdr:row>0</xdr:row>
+                <xdr:rowOff>2</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>2</xdr:col>
+                <xdr:colOff>-265</xdr:colOff>
+                <xdr:row>3</xdr:row>
+                <xdr:rowOff>7</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
     </comment>
     <comment ref="G25" authorId="0">
       <text>
@@ -1742,6 +4703,27 @@
           <t xml:space="preserve">Platform controls available if configured. Evidence: E2</t>
         </r>
       </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>1</xdr:col>
+                <xdr:colOff>35</xdr:colOff>
+                <xdr:row>0</xdr:row>
+                <xdr:rowOff>2</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>2</xdr:col>
+                <xdr:colOff>-265</xdr:colOff>
+                <xdr:row>3</xdr:row>
+                <xdr:rowOff>7</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
     </comment>
     <comment ref="G26" authorId="0">
       <text>
@@ -1754,6 +4736,27 @@
           <t xml:space="preserve">No attack-surface monitoring. Evidence: E4</t>
         </r>
       </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>1</xdr:col>
+                <xdr:colOff>35</xdr:colOff>
+                <xdr:row>0</xdr:row>
+                <xdr:rowOff>2</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>2</xdr:col>
+                <xdr:colOff>-265</xdr:colOff>
+                <xdr:row>3</xdr:row>
+                <xdr:rowOff>7</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
     </comment>
     <comment ref="G27" authorId="0">
       <text>
@@ -1766,6 +4769,27 @@
           <t xml:space="preserve">No device monitoring. Evidence: E4</t>
         </r>
       </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>1</xdr:col>
+                <xdr:colOff>35</xdr:colOff>
+                <xdr:row>0</xdr:row>
+                <xdr:rowOff>2</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>2</xdr:col>
+                <xdr:colOff>-265</xdr:colOff>
+                <xdr:row>3</xdr:row>
+                <xdr:rowOff>7</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
     </comment>
     <comment ref="G28" authorId="0">
       <text>
@@ -1778,6 +4802,27 @@
           <t xml:space="preserve">Contracts may impose vendor wiping (unknown). Evidence: E2</t>
         </r>
       </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>1</xdr:col>
+                <xdr:colOff>35</xdr:colOff>
+                <xdr:row>0</xdr:row>
+                <xdr:rowOff>2</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>2</xdr:col>
+                <xdr:colOff>-265</xdr:colOff>
+                <xdr:row>3</xdr:row>
+                <xdr:rowOff>7</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
     </comment>
     <comment ref="G29" authorId="0">
       <text>
@@ -1790,6 +4835,27 @@
           <t xml:space="preserve">No visibility of AI use. Evidence: E5</t>
         </r>
       </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>1</xdr:col>
+                <xdr:colOff>35</xdr:colOff>
+                <xdr:row>0</xdr:row>
+                <xdr:rowOff>2</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>2</xdr:col>
+                <xdr:colOff>-265</xdr:colOff>
+                <xdr:row>3</xdr:row>
+                <xdr:rowOff>7</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
     </comment>
     <comment ref="G30" authorId="0">
       <text>
@@ -1802,6 +4868,27 @@
           <t xml:space="preserve">MFA change not monitored. Evidence: E7</t>
         </r>
       </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>1</xdr:col>
+                <xdr:colOff>35</xdr:colOff>
+                <xdr:row>0</xdr:row>
+                <xdr:rowOff>2</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>2</xdr:col>
+                <xdr:colOff>-265</xdr:colOff>
+                <xdr:row>3</xdr:row>
+                <xdr:rowOff>7</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
     </comment>
     <comment ref="G31" authorId="0">
       <text>
@@ -1814,6 +4901,27 @@
           <t xml:space="preserve">Key-person dependency; no admin monitoring. Evidence: E3</t>
         </r>
       </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>1</xdr:col>
+                <xdr:colOff>35</xdr:colOff>
+                <xdr:row>0</xdr:row>
+                <xdr:rowOff>2</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>2</xdr:col>
+                <xdr:colOff>-265</xdr:colOff>
+                <xdr:row>3</xdr:row>
+                <xdr:rowOff>7</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
     </comment>
     <comment ref="G32" authorId="0">
       <text>
@@ -1826,6 +4934,27 @@
           <t xml:space="preserve">No integrity checks evidenced. Evidence: E2</t>
         </r>
       </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>1</xdr:col>
+                <xdr:colOff>35</xdr:colOff>
+                <xdr:row>0</xdr:row>
+                <xdr:rowOff>2</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>2</xdr:col>
+                <xdr:colOff>-265</xdr:colOff>
+                <xdr:row>3</xdr:row>
+                <xdr:rowOff>7</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
     </comment>
     <comment ref="G33" authorId="0">
       <text>
@@ -1838,6 +4967,27 @@
           <t xml:space="preserve">Takedown possible once detected. Evidence: E6</t>
         </r>
       </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>1</xdr:col>
+                <xdr:colOff>35</xdr:colOff>
+                <xdr:row>0</xdr:row>
+                <xdr:rowOff>2</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>2</xdr:col>
+                <xdr:colOff>-265</xdr:colOff>
+                <xdr:row>3</xdr:row>
+                <xdr:rowOff>7</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
     </comment>
     <comment ref="H4" authorId="0">
       <text>
@@ -1850,6 +5000,27 @@
           <t xml:space="preserve">Identity is the gateway to every crown jewel. Evidence: E2</t>
         </r>
       </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>1</xdr:col>
+                <xdr:colOff>35</xdr:colOff>
+                <xdr:row>0</xdr:row>
+                <xdr:rowOff>2</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>2</xdr:col>
+                <xdr:colOff>-265</xdr:colOff>
+                <xdr:row>3</xdr:row>
+                <xdr:rowOff>7</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
     </comment>
     <comment ref="H5" authorId="0">
       <text>
@@ -1862,6 +5033,27 @@
           <t xml:space="preserve">EHR and scheduling underpin care delivery. Evidence: E1</t>
         </r>
       </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>1</xdr:col>
+                <xdr:colOff>35</xdr:colOff>
+                <xdr:row>0</xdr:row>
+                <xdr:rowOff>2</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>2</xdr:col>
+                <xdr:colOff>-265</xdr:colOff>
+                <xdr:row>3</xdr:row>
+                <xdr:rowOff>7</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
     </comment>
     <comment ref="H6" authorId="0">
       <text>
@@ -1874,6 +5066,27 @@
           <t xml:space="preserve">Recoverability of every crown jewel depends on it. Evidence: E2</t>
         </r>
       </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>1</xdr:col>
+                <xdr:colOff>35</xdr:colOff>
+                <xdr:row>0</xdr:row>
+                <xdr:rowOff>2</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>2</xdr:col>
+                <xdr:colOff>-265</xdr:colOff>
+                <xdr:row>3</xdr:row>
+                <xdr:rowOff>7</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
     </comment>
     <comment ref="H7" authorId="0">
       <text>
@@ -1886,6 +5099,27 @@
           <t xml:space="preserve">Important but not essential to same-day care. Evidence: E2</t>
         </r>
       </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>1</xdr:col>
+                <xdr:colOff>35</xdr:colOff>
+                <xdr:row>0</xdr:row>
+                <xdr:rowOff>2</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>2</xdr:col>
+                <xdr:colOff>-265</xdr:colOff>
+                <xdr:row>3</xdr:row>
+                <xdr:rowOff>7</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
     </comment>
     <comment ref="H8" authorId="0">
       <text>
@@ -1898,6 +5132,27 @@
           <t xml:space="preserve">EHR confidentiality is core to trust. Evidence: E5</t>
         </r>
       </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>1</xdr:col>
+                <xdr:colOff>35</xdr:colOff>
+                <xdr:row>0</xdr:row>
+                <xdr:rowOff>2</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>2</xdr:col>
+                <xdr:colOff>-265</xdr:colOff>
+                <xdr:row>3</xdr:row>
+                <xdr:rowOff>7</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
     </comment>
     <comment ref="H9" authorId="0">
       <text>
@@ -1910,6 +5165,27 @@
           <t xml:space="preserve">Remote access and perimeter serve all clinics. Evidence: E2</t>
         </r>
       </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>1</xdr:col>
+                <xdr:colOff>35</xdr:colOff>
+                <xdr:row>0</xdr:row>
+                <xdr:rowOff>2</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>2</xdr:col>
+                <xdr:colOff>-265</xdr:colOff>
+                <xdr:row>3</xdr:row>
+                <xdr:rowOff>7</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
     </comment>
     <comment ref="H10" authorId="0">
       <text>
@@ -1922,6 +5198,27 @@
           <t xml:space="preserve">Direct link to patient safety. Evidence: E5</t>
         </r>
       </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>1</xdr:col>
+                <xdr:colOff>35</xdr:colOff>
+                <xdr:row>0</xdr:row>
+                <xdr:rowOff>2</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>2</xdr:col>
+                <xdr:colOff>-265</xdr:colOff>
+                <xdr:row>3</xdr:row>
+                <xdr:rowOff>7</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
     </comment>
     <comment ref="H11" authorId="0">
       <text>
@@ -1934,6 +5231,27 @@
           <t xml:space="preserve">Response capacity protects every service. Evidence: E1</t>
         </r>
       </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>1</xdr:col>
+                <xdr:colOff>35</xdr:colOff>
+                <xdr:row>0</xdr:row>
+                <xdr:rowOff>2</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>2</xdr:col>
+                <xdr:colOff>-265</xdr:colOff>
+                <xdr:row>3</xdr:row>
+                <xdr:rowOff>7</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
     </comment>
     <comment ref="H12" authorId="0">
       <text>
@@ -1946,6 +5264,27 @@
           <t xml:space="preserve">Vendors support crown-jewel systems. Evidence: E2</t>
         </r>
       </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>1</xdr:col>
+                <xdr:colOff>35</xdr:colOff>
+                <xdr:row>0</xdr:row>
+                <xdr:rowOff>2</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>2</xdr:col>
+                <xdr:colOff>-265</xdr:colOff>
+                <xdr:row>3</xdr:row>
+                <xdr:rowOff>7</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
     </comment>
     <comment ref="H13" authorId="0">
       <text>
@@ -1958,6 +5297,27 @@
           <t xml:space="preserve">Clinical record integrity underpins safe care. Evidence: E1</t>
         </r>
       </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>1</xdr:col>
+                <xdr:colOff>35</xdr:colOff>
+                <xdr:row>0</xdr:row>
+                <xdr:rowOff>2</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>2</xdr:col>
+                <xdr:colOff>-265</xdr:colOff>
+                <xdr:row>3</xdr:row>
+                <xdr:rowOff>7</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
     </comment>
     <comment ref="H14" authorId="0">
       <text>
@@ -1970,6 +5330,27 @@
           <t xml:space="preserve">Integrations support EHR and image exchange. Evidence: E2</t>
         </r>
       </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>1</xdr:col>
+                <xdr:colOff>35</xdr:colOff>
+                <xdr:row>0</xdr:row>
+                <xdr:rowOff>2</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>2</xdr:col>
+                <xdr:colOff>-265</xdr:colOff>
+                <xdr:row>3</xdr:row>
+                <xdr:rowOff>7</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
     </comment>
     <comment ref="H15" authorId="0">
       <text>
@@ -1982,6 +5363,27 @@
           <t xml:space="preserve">Clinic networks carry point-of-care EHR access. Evidence: E1</t>
         </r>
       </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>1</xdr:col>
+                <xdr:colOff>35</xdr:colOff>
+                <xdr:row>0</xdr:row>
+                <xdr:rowOff>2</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>2</xdr:col>
+                <xdr:colOff>-265</xdr:colOff>
+                <xdr:row>3</xdr:row>
+                <xdr:rowOff>7</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
     </comment>
     <comment ref="H16" authorId="0">
       <text>
@@ -1994,6 +5396,27 @@
           <t xml:space="preserve">Online services useful but not essential to care. Evidence: E8</t>
         </r>
       </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>1</xdr:col>
+                <xdr:colOff>35</xdr:colOff>
+                <xdr:row>0</xdr:row>
+                <xdr:rowOff>2</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>2</xdr:col>
+                <xdr:colOff>-265</xdr:colOff>
+                <xdr:row>3</xdr:row>
+                <xdr:rowOff>7</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
     </comment>
     <comment ref="H17" authorId="0">
       <text>
@@ -2006,6 +5429,27 @@
           <t xml:space="preserve">Financial, not clinical, process. Evidence: E1</t>
         </r>
       </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>1</xdr:col>
+                <xdr:colOff>35</xdr:colOff>
+                <xdr:row>0</xdr:row>
+                <xdr:rowOff>2</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>2</xdr:col>
+                <xdr:colOff>-265</xdr:colOff>
+                <xdr:row>3</xdr:row>
+                <xdr:rowOff>7</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
     </comment>
     <comment ref="H18" authorId="0">
       <text>
@@ -2018,6 +5462,27 @@
           <t xml:space="preserve">Supports but is not essential to care. Evidence: E2</t>
         </r>
       </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>1</xdr:col>
+                <xdr:colOff>35</xdr:colOff>
+                <xdr:row>0</xdr:row>
+                <xdr:rowOff>2</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>2</xdr:col>
+                <xdr:colOff>-265</xdr:colOff>
+                <xdr:row>3</xdr:row>
+                <xdr:rowOff>7</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
     </comment>
     <comment ref="H19" authorId="0">
       <text>
@@ -2030,6 +5495,27 @@
           <t xml:space="preserve">Hub serves every clinic. Evidence: E2</t>
         </r>
       </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>1</xdr:col>
+                <xdr:colOff>35</xdr:colOff>
+                <xdr:row>0</xdr:row>
+                <xdr:rowOff>2</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>2</xdr:col>
+                <xdr:colOff>-265</xdr:colOff>
+                <xdr:row>3</xdr:row>
+                <xdr:rowOff>7</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
     </comment>
     <comment ref="H20" authorId="0">
       <text>
@@ -2042,6 +5528,27 @@
           <t xml:space="preserve">Supports clinic operations. Evidence: E2</t>
         </r>
       </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>1</xdr:col>
+                <xdr:colOff>35</xdr:colOff>
+                <xdr:row>0</xdr:row>
+                <xdr:rowOff>2</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>2</xdr:col>
+                <xdr:colOff>-265</xdr:colOff>
+                <xdr:row>3</xdr:row>
+                <xdr:rowOff>7</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
     </comment>
     <comment ref="H21" authorId="0">
       <text>
@@ -2054,6 +5561,27 @@
           <t xml:space="preserve">Patient-facing and trust-critical. Evidence: E8</t>
         </r>
       </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>1</xdr:col>
+                <xdr:colOff>35</xdr:colOff>
+                <xdr:row>0</xdr:row>
+                <xdr:rowOff>2</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>2</xdr:col>
+                <xdr:colOff>-265</xdr:colOff>
+                <xdr:row>3</xdr:row>
+                <xdr:rowOff>7</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
     </comment>
     <comment ref="H22" authorId="0">
       <text>
@@ -2066,6 +5594,27 @@
           <t xml:space="preserve">May affect crown-jewel software. Evidence: E2</t>
         </r>
       </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>1</xdr:col>
+                <xdr:colOff>35</xdr:colOff>
+                <xdr:row>0</xdr:row>
+                <xdr:rowOff>2</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>2</xdr:col>
+                <xdr:colOff>-265</xdr:colOff>
+                <xdr:row>3</xdr:row>
+                <xdr:rowOff>7</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
     </comment>
     <comment ref="H23" authorId="0">
       <text>
@@ -2078,6 +5627,27 @@
           <t xml:space="preserve">Cloud identity underpins remote access. Evidence: E2</t>
         </r>
       </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>1</xdr:col>
+                <xdr:colOff>35</xdr:colOff>
+                <xdr:row>0</xdr:row>
+                <xdr:rowOff>2</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>2</xdr:col>
+                <xdr:colOff>-265</xdr:colOff>
+                <xdr:row>3</xdr:row>
+                <xdr:rowOff>7</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
     </comment>
     <comment ref="H24" authorId="0">
       <text>
@@ -2090,6 +5660,27 @@
           <t xml:space="preserve">Routine communication processes. Evidence: E1</t>
         </r>
       </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>1</xdr:col>
+                <xdr:colOff>35</xdr:colOff>
+                <xdr:row>0</xdr:row>
+                <xdr:rowOff>2</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>2</xdr:col>
+                <xdr:colOff>-265</xdr:colOff>
+                <xdr:row>3</xdr:row>
+                <xdr:rowOff>7</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
     </comment>
     <comment ref="H25" authorId="0">
       <text>
@@ -2102,6 +5693,27 @@
           <t xml:space="preserve">Supports but is not core to most care. Evidence: E2</t>
         </r>
       </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>1</xdr:col>
+                <xdr:colOff>35</xdr:colOff>
+                <xdr:row>0</xdr:row>
+                <xdr:rowOff>2</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>2</xdr:col>
+                <xdr:colOff>-265</xdr:colOff>
+                <xdr:row>3</xdr:row>
+                <xdr:rowOff>7</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
     </comment>
     <comment ref="H26" authorId="0">
       <text>
@@ -2114,6 +5726,27 @@
           <t xml:space="preserve">Infrastructure hosts crown jewels. Evidence: E2</t>
         </r>
       </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>1</xdr:col>
+                <xdr:colOff>35</xdr:colOff>
+                <xdr:row>0</xdr:row>
+                <xdr:rowOff>2</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>2</xdr:col>
+                <xdr:colOff>-265</xdr:colOff>
+                <xdr:row>3</xdr:row>
+                <xdr:rowOff>7</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
     </comment>
     <comment ref="H27" authorId="0">
       <text>
@@ -2126,6 +5759,27 @@
           <t xml:space="preserve">Imaging is a core diagnostic service. Evidence: E1</t>
         </r>
       </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>1</xdr:col>
+                <xdr:colOff>35</xdr:colOff>
+                <xdr:row>0</xdr:row>
+                <xdr:rowOff>2</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>2</xdr:col>
+                <xdr:colOff>-265</xdr:colOff>
+                <xdr:row>3</xdr:row>
+                <xdr:rowOff>7</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
     </comment>
     <comment ref="H28" authorId="0">
       <text>
@@ -2138,6 +5792,27 @@
           <t xml:space="preserve">Lifecycle process. Evidence: E2</t>
         </r>
       </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>1</xdr:col>
+                <xdr:colOff>35</xdr:colOff>
+                <xdr:row>0</xdr:row>
+                <xdr:rowOff>2</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>2</xdr:col>
+                <xdr:colOff>-265</xdr:colOff>
+                <xdr:row>3</xdr:row>
+                <xdr:rowOff>7</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
     </comment>
     <comment ref="H29" authorId="0">
       <text>
@@ -2150,6 +5825,27 @@
           <t xml:space="preserve">Clinical documentation. Evidence: E1</t>
         </r>
       </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>1</xdr:col>
+                <xdr:colOff>35</xdr:colOff>
+                <xdr:row>0</xdr:row>
+                <xdr:rowOff>2</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>2</xdr:col>
+                <xdr:colOff>-265</xdr:colOff>
+                <xdr:row>3</xdr:row>
+                <xdr:rowOff>7</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
     </comment>
     <comment ref="H30" authorId="0">
       <text>
@@ -2162,6 +5858,27 @@
           <t xml:space="preserve">Identity gateway. Evidence: E2</t>
         </r>
       </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>1</xdr:col>
+                <xdr:colOff>35</xdr:colOff>
+                <xdr:row>0</xdr:row>
+                <xdr:rowOff>2</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>2</xdr:col>
+                <xdr:colOff>-265</xdr:colOff>
+                <xdr:row>3</xdr:row>
+                <xdr:rowOff>7</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
     </comment>
     <comment ref="H31" authorId="0">
       <text>
@@ -2174,6 +5891,27 @@
           <t xml:space="preserve">Infrastructure-wide. Evidence: E2</t>
         </r>
       </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>1</xdr:col>
+                <xdr:colOff>35</xdr:colOff>
+                <xdr:row>0</xdr:row>
+                <xdr:rowOff>2</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>2</xdr:col>
+                <xdr:colOff>-265</xdr:colOff>
+                <xdr:row>3</xdr:row>
+                <xdr:rowOff>7</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
     </comment>
     <comment ref="H32" authorId="0">
       <text>
@@ -2186,6 +5924,27 @@
           <t xml:space="preserve">Lab and pharmacy data drive treatment. Evidence: E1</t>
         </r>
       </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>1</xdr:col>
+                <xdr:colOff>35</xdr:colOff>
+                <xdr:row>0</xdr:row>
+                <xdr:rowOff>2</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>2</xdr:col>
+                <xdr:colOff>-265</xdr:colOff>
+                <xdr:row>3</xdr:row>
+                <xdr:rowOff>7</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
     </comment>
     <comment ref="H33" authorId="0">
       <text>
@@ -2198,6 +5957,27 @@
           <t xml:space="preserve">Trust and patient communications. Evidence: E5</t>
         </r>
       </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>1</xdr:col>
+                <xdr:colOff>35</xdr:colOff>
+                <xdr:row>0</xdr:row>
+                <xdr:rowOff>2</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>2</xdr:col>
+                <xdr:colOff>-265</xdr:colOff>
+                <xdr:row>3</xdr:row>
+                <xdr:rowOff>7</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
     </comment>
     <comment ref="J4" authorId="0">
       <text>
@@ -2210,6 +5990,27 @@
           <t xml:space="preserve">Representative weakness: remote-access authentication accepting MFA push approval (CWE-308-type single-channel weakness). AV:N internet-reachable gateway; AC:L no special conditions; AT:N; PR:N attacker starts unauthenticated; UI:A user must actively approve; VC/VI:H full session on gateway; VA:N; SC:H EHR data behind the gateway; SI:L/SA:L limited downstream change/disruption. Applicability: moderate - human factor dominates.</t>
         </r>
       </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>1</xdr:col>
+                <xdr:colOff>35</xdr:colOff>
+                <xdr:row>0</xdr:row>
+                <xdr:rowOff>2</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>2</xdr:col>
+                <xdr:colOff>-265</xdr:colOff>
+                <xdr:row>13</xdr:row>
+                <xdr:rowOff>2</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
     </comment>
     <comment ref="J5" authorId="0">
       <text>
@@ -2219,9 +6020,30 @@
             <rFont val="Arial"/>
             <family val="2"/>
           </rPr>
-          <t xml:space="preserve">Representative weakness: malicious macro document leading to code execution (initial vector in E6). AV:N delivered by e-mail; AC:L; AT:N; PR:N; UI:P user opens the document; VC/VI/VA:H on the workstation; SC/SI/SA:H because EHR and clinic systems are subsequently affected. CVSS describes the entry weakness only, not the enterprise impact.</t>
+          <t xml:space="preserve">Representative weakness: malicious macro document leading to code execution (initial vector in E6). AV:L - the document is delivered by e-mail but opened locally on the workstation (FIRST CVSS v4.0 user guide: document-based weaknesses are Local whatever the delivery channel); AC:L; AT:N; PR:N; UI:P user opens the document; VC/VI/VA:H on the workstation; SC/SI/SA:H because EHR and clinic systems are subsequently affected. CVSS describes the entry weakness only, not the enterprise impact.</t>
         </r>
       </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>1</xdr:col>
+                <xdr:colOff>35</xdr:colOff>
+                <xdr:row>0</xdr:row>
+                <xdr:rowOff>2</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>2</xdr:col>
+                <xdr:colOff>-265</xdr:colOff>
+                <xdr:row>14</xdr:row>
+                <xdr:rowOff>31</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
     </comment>
     <comment ref="J6" authorId="0">
       <text>
@@ -2234,6 +6056,27 @@
           <t xml:space="preserve">Representative weakness: backup management console reachable from production network and trusting production administrator accounts. PR:H attacker already holds admin credentials; VC/VI/VA:H on the backup system; SA:H because recovery of all subsequent systems is lost.</t>
         </r>
       </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>1</xdr:col>
+                <xdr:colOff>35</xdr:colOff>
+                <xdr:row>0</xdr:row>
+                <xdr:rowOff>2</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>2</xdr:col>
+                <xdr:colOff>-265</xdr:colOff>
+                <xdr:row>8</xdr:row>
+                <xdr:rowOff>5</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
     </comment>
     <comment ref="J7" authorId="0">
       <text>
@@ -2246,6 +6089,27 @@
           <t xml:space="preserve">Representative weakness: storage object accessible without authentication (CWE-284 misconfiguration). AV:N, AC:L, AT:N, PR:N, UI:N; confidentiality only (VC:H).</t>
         </r>
       </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>1</xdr:col>
+                <xdr:colOff>35</xdr:colOff>
+                <xdr:row>0</xdr:row>
+                <xdr:rowOff>2</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>2</xdr:col>
+                <xdr:colOff>-265</xdr:colOff>
+                <xdr:row>5</xdr:row>
+                <xdr:rowOff>23</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
     </comment>
     <comment ref="J8" authorId="0">
       <text>
@@ -2258,6 +6122,27 @@
           <t xml:space="preserve">Limited applicability: insider misuse is not a software vulnerability. Representative weakness used for the workbook: excessive privileges on an authenticated account (CWE-269). PR:L legitimate low-privilege access; VC:H bulk read; VI:L. Interpret with caution.</t>
         </r>
       </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>1</xdr:col>
+                <xdr:colOff>35</xdr:colOff>
+                <xdr:row>0</xdr:row>
+                <xdr:rowOff>2</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>2</xdr:col>
+                <xdr:colOff>-265</xdr:colOff>
+                <xdr:row>7</xdr:row>
+                <xdr:rowOff>6</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
     </comment>
     <comment ref="J9" authorId="0">
       <text>
@@ -2270,6 +6155,27 @@
           <t xml:space="preserve">Representative weakness: unauthenticated remote code execution in an internet-facing gateway (typical of known-exploited edge vulnerabilities). All impacts High because the gateway fronts the internal network. Replace with the actual CVE vector once scan data is available.</t>
         </r>
       </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>1</xdr:col>
+                <xdr:colOff>35</xdr:colOff>
+                <xdr:row>0</xdr:row>
+                <xdr:rowOff>2</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>2</xdr:col>
+                <xdr:colOff>-265</xdr:colOff>
+                <xdr:row>8</xdr:row>
+                <xdr:rowOff>5</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
     </comment>
     <comment ref="J10" authorId="0">
       <text>
@@ -2282,6 +6188,27 @@
           <t xml:space="preserve">Representative weakness: unpatched embedded service or default credential on a networked device. AV:A reachable from the clinic LAN/Wi-Fi only; PR:N; full device impact; SC/SI/SA:L onward effects. CVSS supplemental metric Safety (S:P) would apply but is not part of the base score.</t>
         </r>
       </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>1</xdr:col>
+                <xdr:colOff>35</xdr:colOff>
+                <xdr:row>0</xdr:row>
+                <xdr:rowOff>2</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>2</xdr:col>
+                <xdr:colOff>-265</xdr:colOff>
+                <xdr:row>7</xdr:row>
+                <xdr:rowOff>21</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
     </comment>
     <comment ref="J11" authorId="0">
       <text>
@@ -2291,9 +6218,30 @@
             <rFont val="Arial"/>
             <family val="2"/>
           </rPr>
-          <t xml:space="preserve">Limited applicability: a detection gap is a control weakness, not a vulnerability. Representative weakness for the workbook: the undetected initial code-execution vector (macro/PowerShell, E6). Do not interpret the score as the severity of the detection gap.</t>
+          <t xml:space="preserve">Limited applicability: a detection gap is a control weakness, not a vulnerability. Representative weakness for the workbook: the undetected initial code-execution vector (macro/PowerShell, E6); AV:L because the malicious document is opened locally. Do not interpret the score as the severity of the detection gap.</t>
         </r>
       </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>1</xdr:col>
+                <xdr:colOff>35</xdr:colOff>
+                <xdr:row>0</xdr:row>
+                <xdr:rowOff>2</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>2</xdr:col>
+                <xdr:colOff>-265</xdr:colOff>
+                <xdr:row>8</xdr:row>
+                <xdr:rowOff>19</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
     </comment>
     <comment ref="J12" authorId="0">
       <text>
@@ -2306,6 +6254,27 @@
           <t xml:space="preserve">Limited applicability: supplier concentration is not a single vulnerability. Representative weakness: standing authenticated remote-access channel. AT:P the vendor must first be compromised; PR:L vendor account; full impacts. Validate against actual vendor access design.</t>
         </r>
       </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>1</xdr:col>
+                <xdr:colOff>35</xdr:colOff>
+                <xdr:row>0</xdr:row>
+                <xdr:rowOff>2</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>2</xdr:col>
+                <xdr:colOff>-265</xdr:colOff>
+                <xdr:row>7</xdr:row>
+                <xdr:rowOff>21</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
     </comment>
     <comment ref="J13" authorId="0">
       <text>
@@ -2318,6 +6287,27 @@
           <t xml:space="preserve">Representative weakness: authenticated user able to modify records beyond need (improper authorization, CWE-285). PR:L; VI:H; SI:H because pharmacy/lab downstream systems consume the altered data.</t>
         </r>
       </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>1</xdr:col>
+                <xdr:colOff>35</xdr:colOff>
+                <xdr:row>0</xdr:row>
+                <xdr:rowOff>2</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>2</xdr:col>
+                <xdr:colOff>-265</xdr:colOff>
+                <xdr:row>6</xdr:row>
+                <xdr:rowOff>22</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
     </comment>
     <comment ref="J14" authorId="0">
       <text>
@@ -2330,6 +6320,27 @@
           <t xml:space="preserve">Representative weakness: hard-coded credential (CWE-798). AT:P the attacker must first obtain the leaked secret; PR:N once held, no further privileges needed; VC:H data access; VI:L limited write scope.</t>
         </r>
       </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>1</xdr:col>
+                <xdr:colOff>35</xdr:colOff>
+                <xdr:row>0</xdr:row>
+                <xdr:rowOff>2</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>2</xdr:col>
+                <xdr:colOff>-265</xdr:colOff>
+                <xdr:row>6</xdr:row>
+                <xdr:rowOff>7</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
     </comment>
     <comment ref="J15" authorId="0">
       <text>
@@ -2342,6 +6353,27 @@
           <t xml:space="preserve">Representative weakness: weak wireless authentication with guest-to-internal routing. AV:A adjacent (radio range); VC/VI:L on the WLAN itself; SC:H clinical systems reachable behind it.</t>
         </r>
       </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>1</xdr:col>
+                <xdr:colOff>35</xdr:colOff>
+                <xdr:row>0</xdr:row>
+                <xdr:rowOff>2</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>2</xdr:col>
+                <xdr:colOff>-265</xdr:colOff>
+                <xdr:row>5</xdr:row>
+                <xdr:rowOff>8</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
     </comment>
     <comment ref="J16" authorId="0">
       <text>
@@ -2354,6 +6386,27 @@
           <t xml:space="preserve">Limited applicability: volumetric DDoS exploits capacity, not a software flaw. Representative weakness: service without rate limiting or upstream mitigation (CWE-770). Availability only.</t>
         </r>
       </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>1</xdr:col>
+                <xdr:colOff>35</xdr:colOff>
+                <xdr:row>0</xdr:row>
+                <xdr:rowOff>2</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>2</xdr:col>
+                <xdr:colOff>-265</xdr:colOff>
+                <xdr:row>5</xdr:row>
+                <xdr:rowOff>23</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
     </comment>
     <comment ref="J17" authorId="0">
       <text>
@@ -2366,6 +6419,27 @@
           <t xml:space="preserve">Limited applicability: payment fraud is a process weakness. Representative weakness: spoofable sender domain without enforced DMARC. UI:A staff must act on the instruction; VI:L data changed. The low score understates business impact - rely on damage estimates.</t>
         </r>
       </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>1</xdr:col>
+                <xdr:colOff>35</xdr:colOff>
+                <xdr:row>0</xdr:row>
+                <xdr:rowOff>2</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>2</xdr:col>
+                <xdr:colOff>-265</xdr:colOff>
+                <xdr:row>7</xdr:row>
+                <xdr:rowOff>6</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
     </comment>
     <comment ref="J18" authorId="0">
       <text>
@@ -2378,6 +6452,27 @@
           <t xml:space="preserve">Representative weakness: missing encryption of sensitive data at rest on the device (CWE-311). AV:P physical possession required; confidentiality only.</t>
         </r>
       </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>1</xdr:col>
+                <xdr:colOff>35</xdr:colOff>
+                <xdr:row>0</xdr:row>
+                <xdr:rowOff>2</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>2</xdr:col>
+                <xdr:colOff>-265</xdr:colOff>
+                <xdr:row>4</xdr:row>
+                <xdr:rowOff>24</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
     </comment>
     <comment ref="J19" authorId="0">
       <text>
@@ -2390,6 +6485,27 @@
           <t xml:space="preserve">Limited applicability: architectural dependency, largely non-malicious. Representative weakness: denial of service against a single edge device with no redundancy (AT:P specific conditions); VA:H and SA:H for downstream systems.</t>
         </r>
       </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>1</xdr:col>
+                <xdr:colOff>35</xdr:colOff>
+                <xdr:row>0</xdr:row>
+                <xdr:rowOff>2</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>2</xdr:col>
+                <xdr:colOff>-265</xdr:colOff>
+                <xdr:row>7</xdr:row>
+                <xdr:rowOff>6</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
     </comment>
     <comment ref="J20" authorId="0">
       <text>
@@ -2402,6 +6518,27 @@
           <t xml:space="preserve">Representative weakness: incorrect default permissions on network shares (CWE-276). AV:A clinic network; PR:L any domain user.</t>
         </r>
       </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>1</xdr:col>
+                <xdr:colOff>35</xdr:colOff>
+                <xdr:row>0</xdr:row>
+                <xdr:rowOff>2</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>2</xdr:col>
+                <xdr:colOff>-265</xdr:colOff>
+                <xdr:row>4</xdr:row>
+                <xdr:rowOff>9</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
     </comment>
     <comment ref="J21" authorId="0">
       <text>
@@ -2414,6 +6551,27 @@
           <t xml:space="preserve">Representative weakness: authorization bypass through user-controlled key (CWE-639). PR:L any patient account; VC:H cross-patient data.</t>
         </r>
       </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>1</xdr:col>
+                <xdr:colOff>35</xdr:colOff>
+                <xdr:row>0</xdr:row>
+                <xdr:rowOff>2</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>2</xdr:col>
+                <xdr:colOff>-265</xdr:colOff>
+                <xdr:row>4</xdr:row>
+                <xdr:rowOff>24</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
     </comment>
     <comment ref="J22" authorId="0">
       <text>
@@ -2426,6 +6584,27 @@
           <t xml:space="preserve">Limited applicability: supplier compromise. Representative weakness: download of code without integrity check (CWE-494). AC:H and AT:P - the supplier's pipeline must be compromised first.</t>
         </r>
       </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>1</xdr:col>
+                <xdr:colOff>35</xdr:colOff>
+                <xdr:row>0</xdr:row>
+                <xdr:rowOff>2</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>2</xdr:col>
+                <xdr:colOff>-265</xdr:colOff>
+                <xdr:row>5</xdr:row>
+                <xdr:rowOff>23</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
     </comment>
     <comment ref="J23" authorId="0">
       <text>
@@ -2438,6 +6617,27 @@
           <t xml:space="preserve">Representative weakness: session token not bound to device, reusable after MFA (CWE-294-type). UI:A admin must interact with the lure; all impacts High because the control plane governs subsequent systems.</t>
         </r>
       </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>1</xdr:col>
+                <xdr:colOff>35</xdr:colOff>
+                <xdr:row>0</xdr:row>
+                <xdr:rowOff>2</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>2</xdr:col>
+                <xdr:colOff>-265</xdr:colOff>
+                <xdr:row>6</xdr:row>
+                <xdr:rowOff>7</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
     </comment>
     <comment ref="J24" authorId="0">
       <text>
@@ -2450,6 +6650,27 @@
           <t xml:space="preserve">Limited applicability: human error. Representative weakness: absence of outbound data-loss safeguards for an authenticated user. The score is low by design; business impact is captured in damage estimates.</t>
         </r>
       </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>1</xdr:col>
+                <xdr:colOff>35</xdr:colOff>
+                <xdr:row>0</xdr:row>
+                <xdr:rowOff>2</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>2</xdr:col>
+                <xdr:colOff>-265</xdr:colOff>
+                <xdr:row>6</xdr:row>
+                <xdr:rowOff>7</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
     </comment>
     <comment ref="J25" authorId="0">
       <text>
@@ -2462,6 +6683,27 @@
           <t xml:space="preserve">Representative weakness: missing authentication for a meeting resource (CWE-306). AT:P attacker must obtain the link.</t>
         </r>
       </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>1</xdr:col>
+                <xdr:colOff>35</xdr:colOff>
+                <xdr:row>0</xdr:row>
+                <xdr:rowOff>2</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>2</xdr:col>
+                <xdr:colOff>-265</xdr:colOff>
+                <xdr:row>4</xdr:row>
+                <xdr:rowOff>9</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
     </comment>
     <comment ref="J26" authorId="0">
       <text>
@@ -2474,6 +6716,27 @@
           <t xml:space="preserve">Representative weakness: exposed management interface with weak or default credentials (CWE-1392/521). AT:P - success depends on a guessable credential.</t>
         </r>
       </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>1</xdr:col>
+                <xdr:colOff>35</xdr:colOff>
+                <xdr:row>0</xdr:row>
+                <xdr:rowOff>2</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>2</xdr:col>
+                <xdr:colOff>-265</xdr:colOff>
+                <xdr:row>4</xdr:row>
+                <xdr:rowOff>24</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
     </comment>
     <comment ref="J27" authorId="0">
       <text>
@@ -2486,6 +6749,27 @@
           <t xml:space="preserve">Representative weakness: automatic execution of content from removable media. AV:P media inserted physically; UI:P staff loads it.</t>
         </r>
       </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>1</xdr:col>
+                <xdr:colOff>35</xdr:colOff>
+                <xdr:row>0</xdr:row>
+                <xdr:rowOff>2</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>2</xdr:col>
+                <xdr:colOff>-265</xdr:colOff>
+                <xdr:row>4</xdr:row>
+                <xdr:rowOff>9</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
     </comment>
     <comment ref="J28" authorId="0">
       <text>
@@ -2498,6 +6782,27 @@
           <t xml:space="preserve">Representative weakness: sensitive information in resource not removed before reuse (CWE-226). AV:P physical possession.</t>
         </r>
       </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>1</xdr:col>
+                <xdr:colOff>35</xdr:colOff>
+                <xdr:row>0</xdr:row>
+                <xdr:rowOff>2</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>2</xdr:col>
+                <xdr:colOff>-265</xdr:colOff>
+                <xdr:row>4</xdr:row>
+                <xdr:rowOff>9</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
     </comment>
     <comment ref="J29" authorId="0">
       <text>
@@ -2510,6 +6815,27 @@
           <t xml:space="preserve">Limited applicability: policy and data-governance gap. Representative weakness: exposure of sensitive information to an unauthorized actor via unrestricted egress (CWE-200). AT:P - harm depends on provider retention.</t>
         </r>
       </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>1</xdr:col>
+                <xdr:colOff>35</xdr:colOff>
+                <xdr:row>0</xdr:row>
+                <xdr:rowOff>2</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>2</xdr:col>
+                <xdr:colOff>-265</xdr:colOff>
+                <xdr:row>6</xdr:row>
+                <xdr:rowOff>22</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
     </comment>
     <comment ref="J30" authorId="0">
       <text>
@@ -2522,6 +6848,27 @@
           <t xml:space="preserve">Limited applicability: process weakness. Representative weakness: weak authentication of the account-recovery process (CWE-640). UI:A help-desk agent acts.</t>
         </r>
       </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>1</xdr:col>
+                <xdr:colOff>35</xdr:colOff>
+                <xdr:row>0</xdr:row>
+                <xdr:rowOff>2</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>2</xdr:col>
+                <xdr:colOff>-265</xdr:colOff>
+                <xdr:row>5</xdr:row>
+                <xdr:rowOff>8</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
     </comment>
     <comment ref="J31" authorId="0">
       <text>
@@ -2534,6 +6881,27 @@
           <t xml:space="preserve">Limited applicability: insider abuse of legitimate privileges. Representative weakness: excessive standing privileges (CWE-250). PR:H administrator.</t>
         </r>
       </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>1</xdr:col>
+                <xdr:colOff>35</xdr:colOff>
+                <xdr:row>0</xdr:row>
+                <xdr:rowOff>2</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>2</xdr:col>
+                <xdr:colOff>-265</xdr:colOff>
+                <xdr:row>4</xdr:row>
+                <xdr:rowOff>24</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
     </comment>
     <comment ref="J32" authorId="0">
       <text>
@@ -2546,6 +6914,27 @@
           <t xml:space="preserve">Representative weakness: cleartext transmission of sensitive information (CWE-319) without integrity check (CWE-353). AV:A adjacent; AT:P attacker must be on path; SI:H downstream EHR.</t>
         </r>
       </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>1</xdr:col>
+                <xdr:colOff>35</xdr:colOff>
+                <xdr:row>0</xdr:row>
+                <xdr:rowOff>2</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>2</xdr:col>
+                <xdr:colOff>-265</xdr:colOff>
+                <xdr:row>5</xdr:row>
+                <xdr:rowOff>23</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
     </comment>
     <comment ref="J33" authorId="0">
       <text>
@@ -2558,6 +6947,27 @@
           <t xml:space="preserve">Limited applicability: impersonation outside MediBec's systems. Representative weakness: sender domain spoofable without enforced DMARC. Business impact is captured by damage estimates, not CVSS.</t>
         </r>
       </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>1</xdr:col>
+                <xdr:colOff>35</xdr:colOff>
+                <xdr:row>0</xdr:row>
+                <xdr:rowOff>2</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>2</xdr:col>
+                <xdr:colOff>-265</xdr:colOff>
+                <xdr:row>6</xdr:row>
+                <xdr:rowOff>7</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
     </comment>
   </commentList>
 </comments>
@@ -2575,7 +6985,7 @@
     <t xml:space="preserve">30-scenario assessment (S1-S10 carried over unchanged from the 10-scenario assessment; S11-S30 added). Source: MediBec Business Case v2.0b (fictional teaching case, M.-A. Leger) and CyberRiskGuardian Excel Guide v1.0c formulas.</t>
   </si>
   <si>
-    <t xml:space="preserve">All parameter values, CVSS vectors, costs and reductions are ANALYST ESTIMATES - VALIDATION REQUIRED. Scores are relative decision-support indicators, not loss predictions.</t>
+    <t xml:space="preserve">All parameter values, CVSS vectors, costs and reductions are ANALYTICAL ESTIMATES — VALIDATION REQUIRED. Scores are relative decision-support indicators, not loss predictions.</t>
   </si>
   <si>
     <t xml:space="preserve">Colour legend:  blue text = input you may edit  |  black = formula  |  green = link to another sheet  |  yellow fill = key assumption.</t>
@@ -2620,7 +7030,7 @@
     <t xml:space="preserve">  Ratio = Residual / Tolerated ;  Cost-effectiveness = (Estimated - Residual) / Cost x 1000</t>
   </si>
   <si>
-    <t xml:space="preserve">Note: the template computes Residual as ABS(L - R). Because both reductions are kept within 0-1, L - R is always &gt;= 0 and the two are identical; a validity check column is included.</t>
+    <t xml:space="preserve">Note: Residual = Estimated - Mitigated; the corrected template guards it with MAX(0, L - R) (never ABS). Both reductions are kept within 0-1, so L - R is always &gt;= 0; a validity check column is included.</t>
   </si>
   <si>
     <t xml:space="preserve">How to use: change blue cells on Parameters / Inputs / Portfolio, then recalculate (Formulas &gt; Calculate Now if manual).</t>
@@ -2641,7 +7051,7 @@
     <t xml:space="preserve">  Budget_Risk    - residual risk and tolerance status at portfolio vs. second-wave funding.</t>
   </si>
   <si>
-    <t xml:space="preserve">Analyse - CyberRiskGuardian KRIs (Excel Guide v1.0c formulas)</t>
+    <t xml:space="preserve">Analyse - CyberRiskGuardian risk indices (Excel Guide v1.0c formulas; not KRIs)</t>
   </si>
   <si>
     <t xml:space="preserve">Green = linked from Inputs / Portfolio / Parameters; black = formula.</t>
@@ -2737,7 +7147,7 @@
     <t xml:space="preserve">Risk appetite (analyst estimate)</t>
   </si>
   <si>
-    <t xml:space="preserve">Analyst estimate - validation required. Case states 0.40 normalized tolerance; see report s.4.</t>
+    <t xml:space="preserve">Analytical estimate — validation required. Case states 0.40 normalized tolerance; see report s.4.</t>
   </si>
   <si>
     <t xml:space="preserve">Multiplication factor</t>
@@ -2776,7 +7186,7 @@
     <t xml:space="preserve">Case escalation - Board acceptance threshold</t>
   </si>
   <si>
-    <t xml:space="preserve">Scenario inputs (0-1 scale unless stated) - Analyst estimates, validation required</t>
+    <t xml:space="preserve">Scenario inputs (0-1 scale unless stated) - Analytical estimates — validation required</t>
   </si>
   <si>
     <t xml:space="preserve">CVSS v4.0 vector</t>
@@ -2824,7 +7234,7 @@
     <t xml:space="preserve">Ransomware disrupting EHR access and clinic operations across the network</t>
   </si>
   <si>
-    <t xml:space="preserve">CVSS:4.0/AV:N/AC:L/AT:N/PR:N/UI:P/VC:H/VI:H/VA:H/SC:H/SI:H/SA:H</t>
+    <t xml:space="preserve">CVSS:4.0/AV:L/AC:L/AT:N/PR:N/UI:P/VC:H/VI:H/VA:H/SC:H/SI:H/SA:H</t>
   </si>
   <si>
     <t xml:space="preserve">S3</t>
@@ -2878,7 +7288,7 @@
     <t xml:space="preserve">Detection and response gaps allow an intrusion to persist and escalate</t>
   </si>
   <si>
-    <t xml:space="preserve">CVSS:4.0/AV:N/AC:L/AT:N/PR:N/UI:P/VC:H/VI:H/VA:L/SC:H/SI:L/SA:L</t>
+    <t xml:space="preserve">CVSS:4.0/AV:L/AC:L/AT:N/PR:N/UI:P/VC:H/VI:H/VA:L/SC:H/SI:L/SA:L</t>
   </si>
   <si>
     <t xml:space="preserve">S9</t>
@@ -3460,7 +7870,7 @@
     <t xml:space="preserve">Allocation assumption: each initiative's Year-1 cost is split equally across the scenarios it addresses, so shared controls are never charged in full to several scenarios.</t>
   </si>
   <si>
-    <t xml:space="preserve">Cyber-insurance premium is excluded (Evidence gap - broker quotation required).</t>
+    <t xml:space="preserve">Cyber-insurance premium is excluded (Information gap - broker quotation required).</t>
   </si>
   <si>
     <t xml:space="preserve">Sensitivity - lower / central / higher cases</t>
@@ -3586,7 +7996,7 @@
     <t xml:space="preserve">Cybercriminal (initial-access broker or ransomware affiliate).</t>
   </si>
   <si>
-    <t xml:space="preserve">Push-based MFA without number matching or phishing resistance (E6 - validate); No evidence of conditional access (geo/device) policies; Internet-sourced macro documents reach users (E6); Awareness programme maturity unknown (Evidence gap)</t>
+    <t xml:space="preserve">Push-based MFA without number matching or phishing resistance (E6 - validate); No evidence of conditional access (geo/device) policies; Internet-sourced macro documents reach users (E6); Awareness programme maturity unknown (Information gap)</t>
   </si>
   <si>
     <t xml:space="preserve">Email filtering / antimalware (E2 - effectiveness unknown); MFA push on remote access (E6); EDR alerting (E6 - triage weak)</t>
@@ -3613,7 +8023,7 @@
     <t xml:space="preserve">Ransomware-as-a-service affiliate (double extortion).</t>
   </si>
   <si>
-    <t xml:space="preserve">Macro execution and weak alert triage (E6); Segmentation between clinics, servers and backups not evidenced (E2, E7); Privileged credential hygiene unknown (Evidence gap); Clinic downtime procedures untested (E7)</t>
+    <t xml:space="preserve">Macro execution and weak alert triage (E6); Segmentation between clinics, servers and backups not evidenced (E2, E7); Privileged credential hygiene unknown (Information gap); Clinic downtime procedures untested (E7)</t>
   </si>
   <si>
     <t xml:space="preserve">Firewalls, IDS/IPS, antimalware (E2); EDR (E6); On-site and off-site backups (E2 - isolation and testing unknown); Incident command structure defined (E6 - untested)</t>
@@ -3631,7 +8041,7 @@
     <t xml:space="preserve">0-24 months</t>
   </si>
   <si>
-    <t xml:space="preserve">Representative weakness: malicious macro document leading to code execution (initial vector in E6). AV:N delivered by e-mail; AC:L; AT:N; PR:N; UI:P user opens the document; VC/VI/VA:H on the workstation; SC/SI/SA:H because EHR and clinic systems are subsequently affected. CVSS describes the entry weakness only, not the enterprise impact.</t>
+    <t xml:space="preserve">Representative weakness: malicious macro document leading to code execution (initial vector in E6). AV:L - the document is delivered by e-mail but opened locally on the workstation (FIRST CVSS v4.0 user guide: document-based weaknesses are Local whatever the delivery channel); AC:L; AT:N; PR:N; UI:P user opens the document; VC/VI/VA:H on the workstation; SC/SI/SA:H because EHR and clinic systems are subsequently affected. CVSS describes the entry weakness only, not the enterprise impact.</t>
   </si>
   <si>
     <t xml:space="preserve">MED-CYR-07</t>
@@ -3727,7 +8137,7 @@
     <t xml:space="preserve">Cybercriminal / state-linked actor using public exploits.</t>
   </si>
   <si>
-    <t xml:space="preserve">Patch SLAs and exception governance not evidenced (E7); Incomplete asset inventory (E4); Possible end-of-life systems (Evidence gap)</t>
+    <t xml:space="preserve">Patch SLAs and exception governance not evidenced (E7); Incomplete asset inventory (E4); Possible end-of-life systems (Information gap)</t>
   </si>
   <si>
     <t xml:space="preserve">Firewalls, IDS/IPS (E2); Antimalware (E2)</t>
@@ -3796,7 +8206,7 @@
     <t xml:space="preserve">I01, I03, I11, I12</t>
   </si>
   <si>
-    <t xml:space="preserve">Limited applicability: a detection gap is a control weakness, not a vulnerability. Representative weakness for the workbook: the undetected initial code-execution vector (macro/PowerShell, E6). Do not interpret the score as the severity of the detection gap.</t>
+    <t xml:space="preserve">Limited applicability: a detection gap is a control weakness, not a vulnerability. Representative weakness for the workbook: the undetected initial code-execution vector (macro/PowerShell, E6); AV:L because the malicious document is opened locally. Do not interpret the score as the severity of the detection gap.</t>
   </si>
   <si>
     <t xml:space="preserve">MED-CYR-14</t>
@@ -3868,7 +8278,7 @@
     <t xml:space="preserve">Opportunistic actor scanning public repositories and paste sites; cybercriminal.</t>
   </si>
   <si>
-    <t xml:space="preserve">No secret scanning or vault evidenced (E7); Long-lived API keys without rotation (Analyst assumption); API calls not monitored for anomalous volume (E7); Development practices and repository visibility unknown (Evidence gap)</t>
+    <t xml:space="preserve">No secret scanning or vault evidenced (E7); Long-lived API keys without rotation (Analyst assumption); API calls not monitored for anomalous volume (E7); Development practices and repository visibility unknown (Information gap)</t>
   </si>
   <si>
     <t xml:space="preserve">Encrypted storage (E2 - does not protect against valid-key access)</t>
@@ -3895,7 +8305,7 @@
     <t xml:space="preserve">Local attacker (visitor, patient, passer-by) or opportunistic cybercriminal.</t>
   </si>
   <si>
-    <t xml:space="preserve">Guest and clinical Wi-Fi segmentation not evidenced (E7); Wireless standard and key management unknown (Evidence gap); No rogue AP detection evidenced; Flat clinic LAN (Analyst assumption, see S7)</t>
+    <t xml:space="preserve">Guest and clinical Wi-Fi segmentation not evidenced (E7); Wireless standard and key management unknown (Information gap); No rogue AP detection evidenced; Flat clinic LAN (Analyst assumption, see S7)</t>
   </si>
   <si>
     <t xml:space="preserve">Firewalls and IDS/IPS at the Montreal hub (E2 - clinic-level coverage unknown)</t>
@@ -6082,7 +10492,7 @@
     <t xml:space="preserve">Methodology</t>
   </si>
   <si>
-    <t xml:space="preserve">Authoritative KRI formulas; CVSS v4.0; multiplication factor 1,000 in worked example; reductions must stay within 0-1.</t>
+    <t xml:space="preserve">Authoritative risk-index formulas; CVSS v4.0; multiplication factor 1,000 in worked example; reductions must stay within 0-1.</t>
   </si>
   <si>
     <t xml:space="preserve">E11</t>
@@ -6112,7 +10522,7 @@
     <t xml:space="preserve">Total IT budget incl. salaries (CAD)</t>
   </si>
   <si>
-    <t xml:space="preserve">Business case s.4 (E3). Evidence gap - appears high for a 15-person IT team; validate with Finance.</t>
+    <t xml:space="preserve">Business case s.4 (E3). Information gap - appears high for a 15-person IT team; validate with Finance.</t>
   </si>
   <si>
     <t xml:space="preserve">Guideline floor - risk seeking (% of IT budget)</t>
@@ -11932,7 +16342,7 @@
         <v>0</v>
       </c>
       <c r="G64" s="38" t="n">
-        <v>800000.000000001</v>
+        <v>800000</v>
       </c>
       <c r="H64" s="38" t="n">
         <v>400000</v>
@@ -11955,7 +16365,7 @@
       </c>
       <c r="M64" s="43" t="n">
         <f aca="false">G64*(1-$E64)</f>
-        <v>640000.000000001</v>
+        <v>640000</v>
       </c>
       <c r="N64" s="43" t="n">
         <f aca="false">H64*(1-$E64)</f>
@@ -13716,11 +18126,11 @@
       </c>
       <c r="C5" s="47" t="n">
         <f aca="false">Analyse!L6</f>
-        <v>7893.48214285714</v>
+        <v>7809.50892857143</v>
       </c>
       <c r="D5" s="47" t="n">
         <f aca="false">Analyse!M6</f>
-        <v>2870.35714285714</v>
+        <v>2839.82142857143</v>
       </c>
       <c r="E5" s="35" t="n">
         <f aca="false">Inputs!K5</f>
@@ -13732,7 +18142,7 @@
       </c>
       <c r="G5" s="48" t="n">
         <f aca="false">C5*(1-E5*F5)</f>
-        <v>3453.3984375</v>
+        <v>3416.66015625</v>
       </c>
       <c r="H5" s="44" t="n">
         <f aca="false">G5/D5</f>
@@ -13750,11 +18160,11 @@
       </c>
       <c r="L5" s="48" t="n">
         <f aca="false">C5*(1-J5*K5)</f>
-        <v>2841.65357142857</v>
+        <v>2811.42321428571</v>
       </c>
       <c r="M5" s="44" t="n">
         <f aca="false">L5/D5</f>
-        <v>0.99</v>
+        <v>0.989999999999999</v>
       </c>
       <c r="N5" s="32" t="str">
         <f aca="false">IF(M5&lt;Parameters!$B$6,"Below tolerance",IF(M5&lt;=Parameters!$B$7,"Approximately at tolerance","Above tolerance"))</f>
@@ -14052,11 +18462,11 @@
       </c>
       <c r="C11" s="47" t="n">
         <f aca="false">Analyse!L12</f>
-        <v>9486</v>
+        <v>9384</v>
       </c>
       <c r="D11" s="47" t="n">
         <f aca="false">Analyse!M12</f>
-        <v>3794.4</v>
+        <v>3753.6</v>
       </c>
       <c r="E11" s="35" t="n">
         <f aca="false">Inputs!K11</f>
@@ -14068,7 +18478,7 @@
       </c>
       <c r="G11" s="48" t="n">
         <f aca="false">C11*(1-E11*F11)</f>
-        <v>4173.84</v>
+        <v>4128.96</v>
       </c>
       <c r="H11" s="44" t="n">
         <f aca="false">G11/D11</f>
@@ -14086,7 +18496,7 @@
       </c>
       <c r="L11" s="48" t="n">
         <f aca="false">C11*(1-J11*K11)</f>
-        <v>3794.4</v>
+        <v>3753.6</v>
       </c>
       <c r="M11" s="44" t="n">
         <f aca="false">L11/D11</f>
@@ -15374,11 +19784,11 @@
       </c>
       <c r="C38" s="48" t="n">
         <f aca="false">SUM(G4:G33)</f>
-        <v>41104.3861752232</v>
+        <v>41022.7678939732</v>
       </c>
       <c r="D38" s="48" t="n">
         <f aca="false">SUM(L4:L33)</f>
-        <v>34136.7923616071</v>
+        <v>34065.7620044643</v>
       </c>
     </row>
   </sheetData>
@@ -15637,7 +20047,7 @@
       </c>
       <c r="E6" s="9" t="n">
         <f aca="false">Inputs!J5</f>
-        <v>9.4</v>
+        <v>9.3</v>
       </c>
       <c r="F6" s="8" t="n">
         <f aca="false">Inputs!E5</f>
@@ -15665,11 +20075,11 @@
       </c>
       <c r="L6" s="11" t="n">
         <f aca="false">C6*D6*E6*((F6+G6)/2)*H6/I6*K6</f>
-        <v>7893.48214285714</v>
+        <v>7809.50892857143</v>
       </c>
       <c r="M6" s="11" t="n">
         <f aca="false">C6*D6*E6*J6*H6/I6*K6</f>
-        <v>2870.35714285714</v>
+        <v>2839.82142857143</v>
       </c>
       <c r="N6" s="12" t="n">
         <f aca="false">L6/M6</f>
@@ -15689,11 +20099,11 @@
       </c>
       <c r="R6" s="11" t="n">
         <f aca="false">L6*P6*Q6</f>
-        <v>4440.08370535714</v>
+        <v>4392.84877232143</v>
       </c>
       <c r="S6" s="11" t="n">
         <f aca="false">L6-R6</f>
-        <v>3453.3984375</v>
+        <v>3416.66015625</v>
       </c>
       <c r="T6" s="12" t="n">
         <f aca="false">S6/M6</f>
@@ -15705,7 +20115,7 @@
       </c>
       <c r="V6" s="12" t="n">
         <f aca="false">IF(O6=0,0,(L6-S6)/O6*1000)</f>
-        <v>12.4600634788693</v>
+        <v>12.3275096120728</v>
       </c>
       <c r="W6" s="14" t="str">
         <f aca="false">IF(AND(P6&gt;=0,P6&lt;=1,Q6&gt;=0,Q6&lt;=1),"OK","CHECK")</f>
@@ -16201,7 +20611,7 @@
       </c>
       <c r="E12" s="9" t="n">
         <f aca="false">Inputs!J11</f>
-        <v>9.3</v>
+        <v>9.2</v>
       </c>
       <c r="F12" s="8" t="n">
         <f aca="false">Inputs!E11</f>
@@ -16229,11 +20639,11 @@
       </c>
       <c r="L12" s="11" t="n">
         <f aca="false">C12*D12*E12*((F12+G12)/2)*H12/I12*K12</f>
-        <v>9486</v>
+        <v>9384</v>
       </c>
       <c r="M12" s="11" t="n">
         <f aca="false">C12*D12*E12*J12*H12/I12*K12</f>
-        <v>3794.4</v>
+        <v>3753.6</v>
       </c>
       <c r="N12" s="12" t="n">
         <f aca="false">L12/M12</f>
@@ -16253,11 +20663,11 @@
       </c>
       <c r="R12" s="11" t="n">
         <f aca="false">L12*P12*Q12</f>
-        <v>5312.16</v>
+        <v>5255.04</v>
       </c>
       <c r="S12" s="11" t="n">
         <f aca="false">L12-R12</f>
-        <v>4173.84</v>
+        <v>4128.96</v>
       </c>
       <c r="T12" s="12" t="n">
         <f aca="false">S12/M12</f>
@@ -16269,7 +20679,7 @@
       </c>
       <c r="V12" s="12" t="n">
         <f aca="false">IF(O12=0,0,(L12-S12)/O12*1000)</f>
-        <v>48.7450166215429</v>
+        <v>48.2208766578704</v>
       </c>
       <c r="W12" s="14" t="str">
         <f aca="false">IF(AND(P12&gt;=0,P12&lt;=1,Q12&gt;=0,Q12&lt;=1),"OK","CHECK")</f>
@@ -18350,11 +22760,11 @@
       </c>
       <c r="L35" s="16" t="n">
         <f aca="false">SUM(L5:L34)</f>
-        <v>84491.4444196429</v>
+        <v>84305.4712053571</v>
       </c>
       <c r="M35" s="16" t="n">
         <f aca="false">SUM(M5:M34)</f>
-        <v>37194.5928571429</v>
+        <v>37123.2571428571</v>
       </c>
       <c r="O35" s="17" t="n">
         <f aca="false">SUM(O5:O34)</f>
@@ -18362,19 +22772,19 @@
       </c>
       <c r="R35" s="16" t="n">
         <f aca="false">SUM(R5:R34)</f>
-        <v>43387.0582444197</v>
+        <v>43282.7033113839</v>
       </c>
       <c r="S35" s="16" t="n">
         <f aca="false">SUM(S5:S34)</f>
-        <v>41104.3861752232</v>
+        <v>41022.7678939732</v>
       </c>
       <c r="T35" s="18" t="n">
         <f aca="false">S35/M35</f>
-        <v>1.1051172500556</v>
+        <v>1.10504225790614</v>
       </c>
       <c r="V35" s="18" t="n">
         <f aca="false">(L35-S35)/O35*1000</f>
-        <v>8.16928229041982</v>
+        <v>8.14963346100243</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -18700,7 +23110,7 @@
         <v>86</v>
       </c>
       <c r="J5" s="23" t="n">
-        <v>9.4</v>
+        <v>9.3</v>
       </c>
       <c r="K5" s="22" t="n">
         <v>0.75</v>
@@ -19036,7 +23446,7 @@
         <v>104</v>
       </c>
       <c r="J11" s="23" t="n">
-        <v>9.3</v>
+        <v>9.2</v>
       </c>
       <c r="K11" s="22" t="n">
         <v>0.7</v>
@@ -23831,7 +28241,7 @@
       </c>
       <c r="J5" s="9" t="n">
         <f aca="false">Inputs!J5</f>
-        <v>9.4</v>
+        <v>9.3</v>
       </c>
       <c r="K5" s="12" t="n">
         <f aca="false">MAX(0.05,MIN(0.99,Inputs!K5-C5))</f>
@@ -23843,15 +28253,15 @@
       </c>
       <c r="M5" s="11" t="n">
         <f aca="false">D5*E5*J5*((F5+G5)/2)*I5/H5*Parameters!$B$5</f>
-        <v>3740.67777777778</v>
+        <v>3700.88333333333</v>
       </c>
       <c r="N5" s="11" t="n">
         <f aca="false">D5*E5*J5*Parameters!$B$4*I5/H5*Parameters!$B$5</f>
-        <v>1547.86666666667</v>
+        <v>1531.4</v>
       </c>
       <c r="O5" s="11" t="n">
         <f aca="false">M5-M5*K5*L5</f>
-        <v>1038.03808333333</v>
+        <v>1026.995125</v>
       </c>
       <c r="P5" s="12" t="n">
         <f aca="false">O5/N5</f>
@@ -23899,7 +28309,7 @@
       </c>
       <c r="J6" s="9" t="n">
         <f aca="false">Inputs!J5</f>
-        <v>9.4</v>
+        <v>9.3</v>
       </c>
       <c r="K6" s="12" t="n">
         <f aca="false">MAX(0.05,MIN(0.99,Inputs!K5-C6))</f>
@@ -23911,15 +28321,15 @@
       </c>
       <c r="M6" s="11" t="n">
         <f aca="false">D6*E6*J6*((F6+G6)/2)*I6/H6*Parameters!$B$5</f>
-        <v>7893.48214285714</v>
+        <v>7809.50892857143</v>
       </c>
       <c r="N6" s="11" t="n">
         <f aca="false">D6*E6*J6*Parameters!$B$4*I6/H6*Parameters!$B$5</f>
-        <v>2870.35714285714</v>
+        <v>2839.82142857143</v>
       </c>
       <c r="O6" s="11" t="n">
         <f aca="false">M6-M6*K6*L6</f>
-        <v>3453.3984375</v>
+        <v>3416.66015625</v>
       </c>
       <c r="P6" s="12" t="n">
         <f aca="false">O6/N6</f>
@@ -23967,7 +28377,7 @@
       </c>
       <c r="J7" s="9" t="n">
         <f aca="false">Inputs!J5</f>
-        <v>9.4</v>
+        <v>9.3</v>
       </c>
       <c r="K7" s="12" t="n">
         <f aca="false">MAX(0.05,MIN(0.99,Inputs!K5-C7))</f>
@@ -23979,15 +28389,15 @@
       </c>
       <c r="M7" s="11" t="n">
         <f aca="false">D7*E7*J7*((F7+G7)/2)*I7/H7*Parameters!$B$5</f>
-        <v>16304.394</v>
+        <v>16130.943</v>
       </c>
       <c r="N7" s="11" t="n">
         <f aca="false">D7*E7*J7*Parameters!$B$4*I7/H7*Parameters!$B$5</f>
-        <v>5465.16</v>
+        <v>5407.02</v>
       </c>
       <c r="O7" s="11" t="n">
         <f aca="false">M7-M7*K7*L7</f>
-        <v>9415.787535</v>
+        <v>9315.6195825</v>
       </c>
       <c r="P7" s="12" t="n">
         <f aca="false">O7/N7</f>
@@ -24035,7 +28445,7 @@
       </c>
       <c r="J8" s="9" t="n">
         <f aca="false">Inputs!J11</f>
-        <v>9.3</v>
+        <v>9.2</v>
       </c>
       <c r="K8" s="12" t="n">
         <f aca="false">MAX(0.05,MIN(0.99,Inputs!K11-C8))</f>
@@ -24047,15 +28457,15 @@
       </c>
       <c r="M8" s="11" t="n">
         <f aca="false">D8*E8*J8*((F8+G8)/2)*I8/H8*Parameters!$B$5</f>
-        <v>4495.96875</v>
+        <v>4447.625</v>
       </c>
       <c r="N8" s="11" t="n">
         <f aca="false">D8*E8*J8*Parameters!$B$4*I8/H8*Parameters!$B$5</f>
-        <v>2075.0625</v>
+        <v>2052.75</v>
       </c>
       <c r="O8" s="11" t="n">
         <f aca="false">M8-M8*K8*L8</f>
-        <v>1258.87125</v>
+        <v>1245.335</v>
       </c>
       <c r="P8" s="12" t="n">
         <f aca="false">O8/N8</f>
@@ -24103,7 +28513,7 @@
       </c>
       <c r="J9" s="9" t="n">
         <f aca="false">Inputs!J11</f>
-        <v>9.3</v>
+        <v>9.2</v>
       </c>
       <c r="K9" s="12" t="n">
         <f aca="false">MAX(0.05,MIN(0.99,Inputs!K11-C9))</f>
@@ -24115,15 +28525,15 @@
       </c>
       <c r="M9" s="11" t="n">
         <f aca="false">D9*E9*J9*((F9+G9)/2)*I9/H9*Parameters!$B$5</f>
-        <v>9486</v>
+        <v>9384</v>
       </c>
       <c r="N9" s="11" t="n">
         <f aca="false">D9*E9*J9*Parameters!$B$4*I9/H9*Parameters!$B$5</f>
-        <v>3794.4</v>
+        <v>3753.6</v>
       </c>
       <c r="O9" s="11" t="n">
         <f aca="false">M9-M9*K9*L9</f>
-        <v>4173.84</v>
+        <v>4128.96</v>
       </c>
       <c r="P9" s="12" t="n">
         <f aca="false">O9/N9</f>
@@ -24171,7 +28581,7 @@
       </c>
       <c r="J10" s="9" t="n">
         <f aca="false">Inputs!J11</f>
-        <v>9.3</v>
+        <v>9.2</v>
       </c>
       <c r="K10" s="12" t="n">
         <f aca="false">MAX(0.05,MIN(0.99,Inputs!K11-C10))</f>
@@ -24183,15 +28593,15 @@
       </c>
       <c r="M10" s="11" t="n">
         <f aca="false">D10*E10*J10*((F10+G10)/2)*I10/H10*Parameters!$B$5</f>
-        <v>21041.13375</v>
+        <v>20814.885</v>
       </c>
       <c r="N10" s="11" t="n">
         <f aca="false">D10*E10*J10*Parameters!$B$4*I10/H10*Parameters!$B$5</f>
-        <v>7470.225</v>
+        <v>7389.9</v>
       </c>
       <c r="O10" s="11" t="n">
         <f aca="false">M10-M10*K10*L10</f>
-        <v>12203.857575</v>
+        <v>12072.6333</v>
       </c>
       <c r="P10" s="12" t="n">
         <f aca="false">O10/N10</f>
@@ -27785,7 +32195,7 @@
         <v>345</v>
       </c>
     </row>
-    <row r="3" customFormat="false" ht="57" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="3" customFormat="false" ht="90.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="21" t="s">
         <v>84</v>
       </c>
